--- a/clic_data.xlsx
+++ b/clic_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luxxx371\Box\Requests\Clic\Administration\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EEE9FFD-9A94-4005-9F3B-F1735852DFEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9154C786-D535-4D89-9BE7-15A77DB2C1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Total Studies" sheetId="8" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2043" uniqueCount="363">
   <si>
     <t>Country</t>
   </si>
@@ -1767,7 +1767,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2130,13 +2130,26 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="27">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2147,7 +2160,35 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3323,7 +3364,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="38" t="s">
         <v>167</v>
       </c>
@@ -3352,7 +3393,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="142.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="71" t="s">
         <v>167</v>
       </c>
@@ -4166,10 +4207,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A54">
-    <cfRule type="containsText" dxfId="21" priority="1" operator="containsText" text="Associate">
+    <cfRule type="containsText" dxfId="26" priority="1" operator="containsText" text="Associate">
       <formula>NOT(ISERROR(SEARCH("Associate",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="2" operator="containsText" text="Full">
+    <cfRule type="containsText" dxfId="25" priority="2" operator="containsText" text="Full">
       <formula>NOT(ISERROR(SEARCH("Full",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5911,19 +5952,19 @@
   </sheetData>
   <autoFilter ref="A1:U25" xr:uid="{3D260CD3-4DAF-439E-9373-903363993C97}"/>
   <conditionalFormatting sqref="E2:S25">
-    <cfRule type="containsText" dxfId="19" priority="1" operator="containsText" text="Imputation">
+    <cfRule type="containsText" dxfId="24" priority="1" operator="containsText" text="Imputation">
       <formula>NOT(ISERROR(SEARCH("Imputation",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="2" operator="containsText" text="Not Applicable">
+    <cfRule type="containsText" dxfId="23" priority="2" operator="containsText" text="Not Applicable">
       <formula>NOT(ISERROR(SEARCH("Not Applicable",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="3" operator="containsText" text="Completed">
+    <cfRule type="containsText" dxfId="22" priority="3" operator="containsText" text="Completed">
       <formula>NOT(ISERROR(SEARCH("Completed",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="4" operator="containsText" text="Ongoing">
+    <cfRule type="containsText" dxfId="21" priority="4" operator="containsText" text="Ongoing">
       <formula>NOT(ISERROR(SEARCH("Ongoing",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="5" operator="containsText" text="Not started">
+    <cfRule type="containsText" dxfId="20" priority="5" operator="containsText" text="Not started">
       <formula>NOT(ISERROR(SEARCH("Not started",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5945,7 +5986,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -6076,11 +6117,11 @@
       <c r="C4" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="D4" s="34" t="s">
-        <v>157</v>
+      <c r="D4" s="31" t="s">
+        <v>156</v>
       </c>
       <c r="E4" s="108" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F4" s="108" t="s">
         <v>348</v>
@@ -6112,11 +6153,11 @@
       <c r="C5" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="D5" s="34" t="s">
-        <v>157</v>
+      <c r="D5" s="31" t="s">
+        <v>156</v>
       </c>
       <c r="E5" s="108" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F5" s="108" t="s">
         <v>348</v>
@@ -6224,7 +6265,7 @@
         <v>156</v>
       </c>
       <c r="E8" s="108" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F8" s="108" t="s">
         <v>348</v>
@@ -6332,7 +6373,7 @@
         <v>156</v>
       </c>
       <c r="E11" s="108" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F11" s="108" t="s">
         <v>348</v>
@@ -6368,7 +6409,7 @@
         <v>156</v>
       </c>
       <c r="E12" s="108" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F12" s="108" t="s">
         <v>348</v>
@@ -6440,7 +6481,7 @@
         <v>156</v>
       </c>
       <c r="E14" s="108" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F14" s="108" t="s">
         <v>348</v>
@@ -6476,7 +6517,7 @@
         <v>156</v>
       </c>
       <c r="E15" s="108" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F15" s="108" t="s">
         <v>348</v>
@@ -6620,7 +6661,7 @@
         <v>156</v>
       </c>
       <c r="E19" s="108" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F19" s="108" t="s">
         <v>348</v>
@@ -6692,7 +6733,7 @@
         <v>156</v>
       </c>
       <c r="E21" s="108" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F21" s="108" t="s">
         <v>348</v>
@@ -6728,7 +6769,7 @@
         <v>156</v>
       </c>
       <c r="E22" s="108" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F22" s="108" t="s">
         <v>348</v>
@@ -6760,8 +6801,8 @@
       <c r="C23" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="D23" s="34" t="s">
-        <v>157</v>
+      <c r="D23" s="31" t="s">
+        <v>156</v>
       </c>
       <c r="E23" s="108" t="s">
         <v>348</v>
@@ -6800,7 +6841,7 @@
         <v>156</v>
       </c>
       <c r="E24" s="108" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F24" s="108" t="s">
         <v>348</v>
@@ -6858,8 +6899,1038 @@
       </c>
       <c r="L25" s="28"/>
     </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="124" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="C26" s="123" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="E26" s="108" t="s">
+        <v>349</v>
+      </c>
+      <c r="F26" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="G26" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="H26" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="I26" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="J26" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="K26" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="L26" s="32"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="E2:K25">
+    <cfRule type="containsText" dxfId="19" priority="6" operator="containsText" text="Imputation">
+      <formula>NOT(ISERROR(SEARCH("Imputation",E2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="18" priority="7" operator="containsText" text="Not Applicable">
+      <formula>NOT(ISERROR(SEARCH("Not Applicable",E2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="17" priority="8" operator="containsText" text="Completed">
+      <formula>NOT(ISERROR(SEARCH("Completed",E2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="16" priority="9" operator="containsText" text="Ongoing">
+      <formula>NOT(ISERROR(SEARCH("Ongoing",E2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="15" priority="10" operator="containsText" text="Not started">
+      <formula>NOT(ISERROR(SEARCH("Not started",E2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E26:K26">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="Imputation">
+      <formula>NOT(ISERROR(SEARCH("Imputation",E26)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Not Applicable">
+      <formula>NOT(ISERROR(SEARCH("Not Applicable",E26)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Completed">
+      <formula>NOT(ISERROR(SEARCH("Completed",E26)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Ongoing">
+      <formula>NOT(ISERROR(SEARCH("Ongoing",E26)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Not started">
+      <formula>NOT(ISERROR(SEARCH("Not started",E26)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:K26" xr:uid="{A555EAE2-07F1-4F5A-B6E3-B3D53739CFEA}">
+      <formula1>"Completed, Ongoing,Not started,Not Applicable,Unknown,Done"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:L26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="35.28515625" customWidth="1"/>
+    <col min="3" max="6" width="26" customWidth="1"/>
+    <col min="7" max="11" width="15" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" s="101" t="s">
+        <v>154</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="G1" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="K1" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="L1" s="27" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="E2" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="F2" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="G2" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="H2" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="I2" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="J2" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="K2" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="L2" s="32"/>
+    </row>
+    <row r="3" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="E3" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="F3" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="G3" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="H3" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="I3" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="J3" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="K3" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="L3" s="32"/>
+    </row>
+    <row r="4" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="E4" s="108" t="s">
+        <v>349</v>
+      </c>
+      <c r="F4" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="G4" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="H4" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="I4" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="J4" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="K4" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="L4" s="32"/>
+    </row>
+    <row r="5" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="E5" s="108" t="s">
+        <v>349</v>
+      </c>
+      <c r="F5" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="G5" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="H5" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="I5" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="J5" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="K5" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="L5" s="32"/>
+    </row>
+    <row r="6" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="E6" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="F6" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="G6" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="H6" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="I6" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="J6" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="K6" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="L6" s="32"/>
+    </row>
+    <row r="7" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="E7" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="F7" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="G7" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="H7" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="I7" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="J7" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="K7" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="L7" s="32"/>
+    </row>
+    <row r="8" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="E8" s="108" t="s">
+        <v>349</v>
+      </c>
+      <c r="F8" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="G8" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="H8" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="I8" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="J8" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="K8" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="L8" s="32"/>
+    </row>
+    <row r="9" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="E9" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="F9" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="G9" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="H9" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="I9" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="J9" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="K9" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="L9" s="32"/>
+    </row>
+    <row r="10" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="E10" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="F10" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="G10" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="H10" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="I10" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="J10" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="K10" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="L10" s="32"/>
+    </row>
+    <row r="11" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="E11" s="108" t="s">
+        <v>349</v>
+      </c>
+      <c r="F11" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="G11" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="H11" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="I11" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="J11" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="K11" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="L11" s="32"/>
+    </row>
+    <row r="12" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="E12" s="108" t="s">
+        <v>349</v>
+      </c>
+      <c r="F12" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="G12" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="H12" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="I12" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="J12" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="K12" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="L12" s="32"/>
+    </row>
+    <row r="13" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="E13" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="F13" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="G13" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="H13" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="I13" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="J13" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="K13" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="L13" s="32"/>
+    </row>
+    <row r="14" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="D14" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="E14" s="108" t="s">
+        <v>349</v>
+      </c>
+      <c r="F14" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="G14" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="H14" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="I14" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="J14" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="K14" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="L14" s="32"/>
+    </row>
+    <row r="15" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="E15" s="108" t="s">
+        <v>349</v>
+      </c>
+      <c r="F15" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="G15" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="H15" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="I15" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="J15" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="K15" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="L15" s="32"/>
+    </row>
+    <row r="16" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="D16" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="E16" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="F16" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="G16" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="H16" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="I16" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="J16" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="K16" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="L16" s="32"/>
+    </row>
+    <row r="17" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="D17" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="E17" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="F17" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="G17" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="H17" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="I17" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="J17" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="K17" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="L17" s="32"/>
+    </row>
+    <row r="18" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="D18" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="E18" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="F18" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="G18" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="H18" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="I18" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="J18" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="K18" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="L18" s="32"/>
+    </row>
+    <row r="19" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="E19" s="108" t="s">
+        <v>349</v>
+      </c>
+      <c r="F19" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="G19" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="H19" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="I19" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="J19" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="K19" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="L19" s="32"/>
+    </row>
+    <row r="20" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="E20" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="F20" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="G20" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="H20" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="I20" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="J20" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="K20" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="L20" s="32"/>
+    </row>
+    <row r="21" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="D21" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="E21" s="108" t="s">
+        <v>349</v>
+      </c>
+      <c r="F21" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="G21" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="H21" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="I21" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="J21" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="K21" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="L21" s="32"/>
+    </row>
+    <row r="22" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="D22" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="E22" s="108" t="s">
+        <v>349</v>
+      </c>
+      <c r="F22" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="G22" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="H22" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="I22" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="J22" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="K22" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="L22" s="32"/>
+    </row>
+    <row r="23" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="E23" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="F23" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="G23" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="H23" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="I23" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="J23" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="K23" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="L23" s="32"/>
+    </row>
+    <row r="24" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="D24" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="E24" s="108" t="s">
+        <v>349</v>
+      </c>
+      <c r="F24" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="G24" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="H24" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="I24" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="J24" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="K24" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="L24" s="32"/>
+    </row>
+    <row r="25" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="D25" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="E25" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="F25" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="G25" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="H25" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="I25" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="J25" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="K25" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="L25" s="32"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="124" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="C26" s="123" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="E26" s="108" t="s">
+        <v>349</v>
+      </c>
+      <c r="F26" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="G26" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="H26" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="I26" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="J26" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="K26" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="L26" s="32"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="E2:K26">
     <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="Imputation">
       <formula>NOT(ISERROR(SEARCH("Imputation",E2)))</formula>
     </cfRule>
@@ -6877,948 +7948,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:K25" xr:uid="{A555EAE2-07F1-4F5A-B6E3-B3D53739CFEA}">
-      <formula1>"Completed, Ongoing,Not started,Not Applicable,Unknown,Done"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="35.28515625" customWidth="1"/>
-    <col min="3" max="6" width="26" customWidth="1"/>
-    <col min="7" max="11" width="15" customWidth="1"/>
-    <col min="12" max="12" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="C1" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="D1" s="101" t="s">
-        <v>154</v>
-      </c>
-      <c r="E1" s="27" t="s">
-        <v>152</v>
-      </c>
-      <c r="F1" s="27" t="s">
-        <v>153</v>
-      </c>
-      <c r="G1" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="H1" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="I1" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="J1" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="K1" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="L1" s="27" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="B2" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="C2" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="D2" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="E2" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="F2" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="G2" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="H2" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="I2" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="J2" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="K2" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="L2" s="32"/>
-    </row>
-    <row r="3" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="C3" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="D3" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="E3" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="F3" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="G3" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="H3" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="I3" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="J3" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="K3" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="L3" s="32"/>
-    </row>
-    <row r="4" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="C4" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>157</v>
-      </c>
-      <c r="E4" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="F4" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="G4" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="H4" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="I4" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="J4" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="K4" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="L4" s="32"/>
-    </row>
-    <row r="5" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="D5" s="34" t="s">
-        <v>157</v>
-      </c>
-      <c r="E5" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="F5" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="G5" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="H5" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="I5" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="J5" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="K5" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="L5" s="32"/>
-    </row>
-    <row r="6" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="E6" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="F6" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="G6" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="H6" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="I6" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="J6" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="K6" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="L6" s="32"/>
-    </row>
-    <row r="7" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="C7" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="D7" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="E7" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="F7" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="G7" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="H7" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="I7" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="J7" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="K7" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="L7" s="32"/>
-    </row>
-    <row r="8" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="E8" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="F8" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="G8" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="H8" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="I8" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="J8" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="K8" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="L8" s="32"/>
-    </row>
-    <row r="9" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="E9" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="F9" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="G9" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="H9" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="I9" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="J9" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="K9" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="L9" s="32"/>
-    </row>
-    <row r="10" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="E10" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="F10" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="G10" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="H10" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="I10" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="J10" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="K10" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="L10" s="32"/>
-    </row>
-    <row r="11" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="C11" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="E11" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="F11" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="G11" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="H11" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="I11" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="J11" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="K11" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="L11" s="32"/>
-    </row>
-    <row r="12" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="B12" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="E12" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="F12" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="G12" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="H12" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="I12" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="J12" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="K12" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="L12" s="32"/>
-    </row>
-    <row r="13" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="C13" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="E13" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="F13" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="G13" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="H13" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="I13" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="J13" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="K13" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="L13" s="32"/>
-    </row>
-    <row r="14" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="B14" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="E14" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="F14" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="G14" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="H14" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="I14" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="J14" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="K14" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="L14" s="32"/>
-    </row>
-    <row r="15" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="C15" s="30" t="s">
-        <v>113</v>
-      </c>
-      <c r="D15" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="E15" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="F15" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="G15" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="H15" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="I15" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="J15" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="K15" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="L15" s="32"/>
-    </row>
-    <row r="16" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="D16" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="E16" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="F16" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="G16" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="H16" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="I16" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="J16" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="K16" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="L16" s="32"/>
-    </row>
-    <row r="17" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="C17" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="D17" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="E17" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="F17" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="G17" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="H17" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="I17" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="J17" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="K17" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="L17" s="32"/>
-    </row>
-    <row r="18" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="B18" s="25" t="s">
-        <v>129</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>115</v>
-      </c>
-      <c r="D18" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="E18" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="F18" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="G18" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="H18" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="I18" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="J18" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="K18" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="L18" s="32"/>
-    </row>
-    <row r="19" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="25" t="s">
-        <v>130</v>
-      </c>
-      <c r="C19" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="E19" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="F19" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="G19" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="H19" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="I19" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="J19" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="K19" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="L19" s="32"/>
-    </row>
-    <row r="20" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="B20" s="25" t="s">
-        <v>131</v>
-      </c>
-      <c r="C20" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="E20" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="F20" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="G20" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="H20" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="I20" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="J20" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="K20" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="L20" s="32"/>
-    </row>
-    <row r="21" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="C21" s="30" t="s">
-        <v>116</v>
-      </c>
-      <c r="D21" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="E21" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="F21" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="G21" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="H21" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="I21" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="J21" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="K21" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="L21" s="32"/>
-    </row>
-    <row r="22" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="D22" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="E22" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="F22" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="G22" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="H22" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="I22" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="J22" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="K22" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="L22" s="32"/>
-    </row>
-    <row r="23" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="C23" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="D23" s="34" t="s">
-        <v>157</v>
-      </c>
-      <c r="E23" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="F23" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="G23" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="H23" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="I23" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="J23" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="K23" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="L23" s="32"/>
-    </row>
-    <row r="24" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="D24" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="E24" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="F24" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="G24" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="H24" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="I24" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="J24" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="K24" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="L24" s="32"/>
-    </row>
-    <row r="25" spans="1:12" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="B25" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="C25" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="D25" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="E25" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="F25" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="G25" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="H25" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="I25" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="J25" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="K25" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="L25" s="32"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="E2:K25">
-    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="Imputation">
-      <formula>NOT(ISERROR(SEARCH("Imputation",E2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="Not Applicable">
-      <formula>NOT(ISERROR(SEARCH("Not Applicable",E2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="3" operator="containsText" text="Completed">
-      <formula>NOT(ISERROR(SEARCH("Completed",E2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="4" operator="containsText" text="Ongoing">
-      <formula>NOT(ISERROR(SEARCH("Ongoing",E2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="Not started">
-      <formula>NOT(ISERROR(SEARCH("Not started",E2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:K25" xr:uid="{AD093F45-6044-45B6-A91C-B146170D7F21}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:K26" xr:uid="{AD093F45-6044-45B6-A91C-B146170D7F21}">
       <formula1>"Completed, Ongoing,Not started,Not Applicable,Unknown,Done"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9366,19 +9496,19 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:I51">
-    <cfRule type="beginsWith" dxfId="4" priority="1" operator="beginsWith" text="Complete">
+    <cfRule type="beginsWith" dxfId="9" priority="1" operator="beginsWith" text="Complete">
       <formula>LEFT(C2,LEN("Complete"))="Complete"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Planned">
+    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="Planned">
       <formula>NOT(ISERROR(SEARCH("Planned",C2)))</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="2" priority="3" operator="beginsWith" text="Incomplete">
+    <cfRule type="beginsWith" dxfId="7" priority="3" operator="beginsWith" text="Incomplete">
       <formula>LEFT(C2,LEN("Incomplete"))="Incomplete"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Not Applicable">
+    <cfRule type="containsText" dxfId="6" priority="4" operator="containsText" text="Not Applicable">
       <formula>NOT(ISERROR(SEARCH("Not Applicable",C2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="Unknown">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="Unknown">
       <formula>NOT(ISERROR(SEARCH("Unknown",C2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/clic_data.xlsx
+++ b/clic_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luxxx371\Box\Requests\Clic\Administration\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C34A926-2F1C-40AF-B65F-3E627CD68EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1CD1A7-15A0-45F6-B49C-9DC725A211D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Total Studies" sheetId="8" r:id="rId1"/>
@@ -23,7 +23,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Genomic Pipeline'!$A$1:$W$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Phenotype Data'!$A$1:$L$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Total Studies'!$A$1:$I$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Total Studies'!$A$1:$I$55</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2148" uniqueCount="376">
   <si>
     <t>Country</t>
   </si>
@@ -915,9 +915,6 @@
     <t>2004-2015 (ongoing)</t>
   </si>
   <si>
-    <t>Maybe?</t>
-  </si>
-  <si>
     <t>PeiChen Lee</t>
   </si>
   <si>
@@ -1183,13 +1180,25 @@
   </si>
   <si>
     <t>Planned</t>
+  </si>
+  <si>
+    <t>Soutsh Mexican study</t>
+  </si>
+  <si>
+    <t>Juan Carlos Núñez-Enríquez</t>
+  </si>
+  <si>
+    <t>2021 to 2023</t>
+  </si>
+  <si>
+    <t>SMS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1316,6 +1325,12 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Open Sans"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1793,7 +1808,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2169,89 +2184,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="23">
     <dxf>
       <fill>
         <patternFill>
@@ -2354,6 +2293,48 @@
       <fill>
         <patternFill>
           <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2671,8 +2652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{653AF72C-24C0-4E60-8663-786F0182C4B9}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="18.28515625" customWidth="1"/>
@@ -2708,7 +2688,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="37" t="s">
         <v>167</v>
       </c>
@@ -2737,7 +2717,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="42" t="s">
         <v>167</v>
       </c>
@@ -2766,7 +2746,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="32.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="42" t="s">
         <v>167</v>
       </c>
@@ -2795,7 +2775,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="48" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="42" t="s">
         <v>167</v>
       </c>
@@ -2824,7 +2804,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="48" t="s">
         <v>167</v>
       </c>
@@ -2853,7 +2833,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="126.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="50" t="s">
         <v>186</v>
       </c>
@@ -2882,7 +2862,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="48" t="s">
         <v>167</v>
       </c>
@@ -2911,7 +2891,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="95.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="95.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="48" t="s">
         <v>186</v>
       </c>
@@ -2940,7 +2920,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="32.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="48" t="s">
         <v>186</v>
       </c>
@@ -2969,7 +2949,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="32.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="48" t="s">
         <v>186</v>
       </c>
@@ -2998,7 +2978,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="63.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="37" t="s">
         <v>167</v>
       </c>
@@ -3027,7 +3007,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="142.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="142.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="37" t="s">
         <v>167</v>
       </c>
@@ -3056,7 +3036,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="63.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="48" t="s">
         <v>167</v>
       </c>
@@ -3085,7 +3065,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="48" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="50" t="s">
         <v>167</v>
       </c>
@@ -3114,7 +3094,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="95.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="95.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="37" t="s">
         <v>167</v>
       </c>
@@ -3143,7 +3123,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="48" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="37" t="s">
         <v>167</v>
       </c>
@@ -3172,7 +3152,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="37" t="s">
         <v>167</v>
       </c>
@@ -3201,7 +3181,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="37" t="s">
         <v>167</v>
       </c>
@@ -3230,7 +3210,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="45.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="37" t="s">
         <v>167</v>
       </c>
@@ -3259,7 +3239,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="60.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="37" t="s">
         <v>167</v>
       </c>
@@ -3288,7 +3268,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="32.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="37" t="s">
         <v>186</v>
       </c>
@@ -3317,7 +3297,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="95.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="95.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="37" t="s">
         <v>167</v>
       </c>
@@ -3346,7 +3326,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="111" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A24" s="60" t="s">
         <v>167</v>
       </c>
@@ -3375,7 +3355,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="111" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="111" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="50" t="s">
         <v>186</v>
       </c>
@@ -3404,7 +3384,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="32.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="37" t="s">
         <v>167</v>
       </c>
@@ -3433,7 +3413,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="79.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="70" t="s">
         <v>167</v>
       </c>
@@ -3462,7 +3442,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="48" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="37" t="s">
         <v>186</v>
       </c>
@@ -3491,7 +3471,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="126.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="48" t="s">
         <v>186</v>
       </c>
@@ -3520,7 +3500,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="126.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="70" t="s">
         <v>167</v>
       </c>
@@ -3549,212 +3529,212 @@
         <v>267</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="63.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="48" t="s">
+    <row r="31" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="70" t="s">
         <v>167</v>
       </c>
-      <c r="B31" s="38" t="s">
+      <c r="B31" s="76" t="s">
+        <v>206</v>
+      </c>
+      <c r="C31" s="77" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="70" t="s">
+        <v>372</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="F31" s="127" t="s">
+        <v>374</v>
+      </c>
+      <c r="G31" s="74" t="s">
+        <v>229</v>
+      </c>
+      <c r="H31" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="I31" s="70" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="48" t="s">
+        <v>167</v>
+      </c>
+      <c r="B32" s="38" t="s">
         <v>168</v>
       </c>
-      <c r="C31" s="39" t="s">
+      <c r="C32" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="D31" s="37" t="s">
+      <c r="D32" s="37" t="s">
         <v>268</v>
-      </c>
-      <c r="E31" s="40" t="s">
-        <v>213</v>
-      </c>
-      <c r="F31" s="40" t="s">
-        <v>269</v>
-      </c>
-      <c r="G31" s="41" t="s">
-        <v>234</v>
-      </c>
-      <c r="H31" s="41" t="s">
-        <v>156</v>
-      </c>
-      <c r="I31" s="37" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="75.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="78" t="s">
-        <v>186</v>
-      </c>
-      <c r="B32" s="79" t="s">
-        <v>260</v>
-      </c>
-      <c r="C32" s="80" t="s">
-        <v>36</v>
-      </c>
-      <c r="D32" s="40" t="s">
-        <v>271</v>
       </c>
       <c r="E32" s="40" t="s">
         <v>213</v>
       </c>
       <c r="F32" s="40" t="s">
+        <v>269</v>
+      </c>
+      <c r="G32" s="41" t="s">
+        <v>234</v>
+      </c>
+      <c r="H32" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I32" s="37" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="78" t="s">
+        <v>186</v>
+      </c>
+      <c r="B33" s="79" t="s">
+        <v>260</v>
+      </c>
+      <c r="C33" s="80" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33" s="40" t="s">
+        <v>271</v>
+      </c>
+      <c r="E33" s="40" t="s">
+        <v>213</v>
+      </c>
+      <c r="F33" s="40" t="s">
         <v>272</v>
       </c>
-      <c r="G32" s="81" t="s">
+      <c r="G33" s="81" t="s">
         <v>273</v>
       </c>
-      <c r="H32" s="81" t="s">
+      <c r="H33" s="81" t="s">
         <v>157</v>
       </c>
-      <c r="I32" s="40" t="s">
+      <c r="I33" s="40" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="82" t="s">
+    <row r="34" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="82" t="s">
         <v>186</v>
       </c>
-      <c r="B33" s="83" t="s">
+      <c r="B34" s="83" t="s">
         <v>211</v>
       </c>
-      <c r="C33" s="84" t="s">
+      <c r="C34" s="84" t="s">
         <v>39</v>
       </c>
-      <c r="D33" s="85" t="s">
+      <c r="D34" s="85" t="s">
         <v>275</v>
       </c>
-      <c r="E33" s="53" t="s">
+      <c r="E34" s="53" t="s">
         <v>213</v>
       </c>
-      <c r="F33" s="53" t="s">
+      <c r="F34" s="53" t="s">
         <v>276</v>
       </c>
-      <c r="G33" s="86" t="s">
+      <c r="G34" s="86" t="s">
         <v>273</v>
       </c>
-      <c r="H33" s="86" t="s">
+      <c r="H34" s="86" t="s">
         <v>157</v>
       </c>
-      <c r="I33" s="53" t="s">
+      <c r="I34" s="53" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="126.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="48" t="s">
+    <row r="35" spans="1:9" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="48" t="s">
         <v>186</v>
       </c>
-      <c r="B34" s="87" t="s">
+      <c r="B35" s="87" t="s">
         <v>211</v>
       </c>
-      <c r="C34" s="39" t="s">
+      <c r="C35" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="D34" s="37" t="s">
+      <c r="D35" s="37" t="s">
         <v>278</v>
-      </c>
-      <c r="E34" s="40" t="s">
-        <v>169</v>
-      </c>
-      <c r="F34" s="40" t="s">
-        <v>279</v>
-      </c>
-      <c r="G34" s="41" t="s">
-        <v>190</v>
-      </c>
-      <c r="H34" s="41" t="s">
-        <v>157</v>
-      </c>
-      <c r="I34" s="37" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="126.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="48" t="s">
-        <v>167</v>
-      </c>
-      <c r="B35" s="75" t="s">
-        <v>260</v>
-      </c>
-      <c r="C35" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D35" s="37" t="s">
-        <v>281</v>
       </c>
       <c r="E35" s="40" t="s">
         <v>169</v>
       </c>
       <c r="F35" s="40" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G35" s="41" t="s">
         <v>190</v>
       </c>
       <c r="H35" s="41" t="s">
-        <v>283</v>
+        <v>157</v>
       </c>
       <c r="I35" s="37" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="60.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="78" t="s">
-        <v>186</v>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="48" t="s">
+        <v>167</v>
       </c>
       <c r="B36" s="75" t="s">
         <v>260</v>
       </c>
-      <c r="C36" s="80" t="s">
+      <c r="C36" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D36" s="40" t="s">
+      <c r="D36" s="37" t="s">
+        <v>281</v>
+      </c>
+      <c r="E36" s="40" t="s">
+        <v>169</v>
+      </c>
+      <c r="F36" s="40" t="s">
+        <v>282</v>
+      </c>
+      <c r="G36" s="41" t="s">
+        <v>190</v>
+      </c>
+      <c r="H36" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="I36" s="37" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="78" t="s">
+        <v>186</v>
+      </c>
+      <c r="B37" s="75" t="s">
+        <v>260</v>
+      </c>
+      <c r="C37" s="80" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37" s="40" t="s">
+        <v>284</v>
+      </c>
+      <c r="E37" s="40" t="s">
         <v>285</v>
       </c>
-      <c r="E36" s="40" t="s">
+      <c r="F37" s="40" t="s">
+        <v>197</v>
+      </c>
+      <c r="G37" s="88" t="s">
         <v>286</v>
       </c>
-      <c r="F36" s="40" t="s">
-        <v>197</v>
-      </c>
-      <c r="G36" s="88" t="s">
-        <v>287</v>
-      </c>
-      <c r="H36" s="81" t="s">
-        <v>5</v>
-      </c>
-      <c r="I36" s="40" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="48" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="48" t="s">
+      <c r="H37" s="81" t="s">
+        <v>5</v>
+      </c>
+      <c r="I37" s="40" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="48" t="s">
         <v>167</v>
-      </c>
-      <c r="B37" s="57" t="s">
-        <v>211</v>
-      </c>
-      <c r="C37" s="39" t="s">
-        <v>137</v>
-      </c>
-      <c r="D37" s="37" t="s">
-        <v>288</v>
-      </c>
-      <c r="E37" s="40" t="s">
-        <v>213</v>
-      </c>
-      <c r="F37" s="40" t="s">
-        <v>289</v>
-      </c>
-      <c r="G37" s="41" t="s">
-        <v>234</v>
-      </c>
-      <c r="H37" s="41" t="s">
-        <v>156</v>
-      </c>
-      <c r="I37" s="37" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="63.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="48" t="s">
-        <v>186</v>
       </c>
       <c r="B38" s="57" t="s">
         <v>211</v>
@@ -3763,25 +3743,25 @@
         <v>137</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E38" s="40" t="s">
-        <v>5</v>
+        <v>213</v>
       </c>
       <c r="F38" s="40" t="s">
-        <v>5</v>
+        <v>288</v>
       </c>
       <c r="G38" s="41" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="H38" s="41" t="s">
-        <v>5</v>
+        <v>156</v>
       </c>
       <c r="I38" s="37" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="32.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="48" t="s">
         <v>186</v>
       </c>
@@ -3792,54 +3772,54 @@
         <v>137</v>
       </c>
       <c r="D39" s="37" t="s">
+        <v>290</v>
+      </c>
+      <c r="E39" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="F39" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="G39" s="41" t="s">
+        <v>220</v>
+      </c>
+      <c r="H39" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="I39" s="37" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="48" t="s">
+        <v>186</v>
+      </c>
+      <c r="B40" s="57" t="s">
+        <v>211</v>
+      </c>
+      <c r="C40" s="39" t="s">
+        <v>137</v>
+      </c>
+      <c r="D40" s="37" t="s">
+        <v>291</v>
+      </c>
+      <c r="E40" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="F40" s="40" t="s">
         <v>292</v>
       </c>
-      <c r="E39" s="40" t="s">
-        <v>182</v>
-      </c>
-      <c r="F39" s="40" t="s">
+      <c r="G40" s="41">
+        <v>2013</v>
+      </c>
+      <c r="H40" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="I40" s="37" t="s">
         <v>293</v>
       </c>
-      <c r="G39" s="41">
-        <v>2013</v>
-      </c>
-      <c r="H39" s="41" t="s">
-        <v>283</v>
-      </c>
-      <c r="I39" s="37" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="48" t="s">
-        <v>167</v>
-      </c>
-      <c r="B40" s="55" t="s">
-        <v>192</v>
-      </c>
-      <c r="C40" s="80" t="s">
-        <v>80</v>
-      </c>
-      <c r="D40" s="37" t="s">
-        <v>295</v>
-      </c>
-      <c r="E40" s="40" t="s">
-        <v>169</v>
-      </c>
-      <c r="F40" s="40" t="s">
-        <v>296</v>
-      </c>
-      <c r="G40" s="41" t="s">
-        <v>171</v>
-      </c>
-      <c r="H40" s="41" t="s">
-        <v>156</v>
-      </c>
-      <c r="I40" s="37" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="111" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:9" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="48" t="s">
         <v>167</v>
       </c>
@@ -3850,25 +3830,25 @@
         <v>80</v>
       </c>
       <c r="D41" s="37" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="E41" s="40" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="F41" s="40" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="G41" s="41" t="s">
-        <v>300</v>
+        <v>171</v>
       </c>
       <c r="H41" s="41" t="s">
         <v>156</v>
       </c>
       <c r="I41" s="37" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="111" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="48" t="s">
         <v>167</v>
       </c>
@@ -3879,22 +3859,22 @@
         <v>80</v>
       </c>
       <c r="D42" s="37" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="E42" s="40" t="s">
         <v>182</v>
       </c>
       <c r="F42" s="40" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="G42" s="41" t="s">
-        <v>234</v>
+        <v>299</v>
       </c>
       <c r="H42" s="41" t="s">
         <v>156</v>
       </c>
       <c r="I42" s="37" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3908,25 +3888,25 @@
         <v>80</v>
       </c>
       <c r="D43" s="37" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="E43" s="40" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="F43" s="40" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="G43" s="41" t="s">
-        <v>307</v>
+        <v>234</v>
       </c>
       <c r="H43" s="41" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I43" s="37" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="48" t="s">
         <v>167</v>
       </c>
@@ -3937,25 +3917,25 @@
         <v>80</v>
       </c>
       <c r="D44" s="37" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="E44" s="40" t="s">
         <v>169</v>
       </c>
       <c r="F44" s="40" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="G44" s="41" t="s">
-        <v>220</v>
+        <v>306</v>
       </c>
       <c r="H44" s="41" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I44" s="37" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="95.25" thickBot="1" x14ac:dyDescent="0.3">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="48" t="s">
         <v>167</v>
       </c>
@@ -3966,112 +3946,112 @@
         <v>80</v>
       </c>
       <c r="D45" s="37" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E45" s="40" t="s">
-        <v>213</v>
+        <v>169</v>
       </c>
       <c r="F45" s="40" t="s">
-        <v>313</v>
-      </c>
-      <c r="G45" s="41">
-        <v>2011</v>
+        <v>309</v>
+      </c>
+      <c r="G45" s="41" t="s">
+        <v>220</v>
       </c>
       <c r="H45" s="41" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I45" s="37" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="78" t="s">
-        <v>186</v>
-      </c>
-      <c r="B46" s="79" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="95.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="48" t="s">
+        <v>167</v>
+      </c>
+      <c r="B46" s="55" t="s">
         <v>192</v>
       </c>
       <c r="C46" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="D46" s="40" t="s">
-        <v>82</v>
+      <c r="D46" s="37" t="s">
+        <v>311</v>
       </c>
       <c r="E46" s="40" t="s">
-        <v>315</v>
+        <v>213</v>
       </c>
       <c r="F46" s="40" t="s">
-        <v>316</v>
-      </c>
-      <c r="G46" s="81" t="s">
-        <v>287</v>
-      </c>
-      <c r="H46" s="81" t="s">
-        <v>5</v>
-      </c>
-      <c r="I46" s="40" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="G46" s="41">
+        <v>2011</v>
+      </c>
+      <c r="H46" s="41" t="s">
+        <v>157</v>
+      </c>
+      <c r="I46" s="37" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="78" t="s">
         <v>186</v>
       </c>
       <c r="B47" s="79" t="s">
         <v>192</v>
       </c>
-      <c r="C47" s="89" t="s">
+      <c r="C47" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="D47" s="20" t="s">
+      <c r="D47" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="E47" s="40" t="s">
+        <v>314</v>
+      </c>
+      <c r="F47" s="40" t="s">
+        <v>315</v>
+      </c>
+      <c r="G47" s="81" t="s">
+        <v>286</v>
+      </c>
+      <c r="H47" s="81" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="40" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="B48" s="79" t="s">
+        <v>192</v>
+      </c>
+      <c r="C48" s="89" t="s">
+        <v>80</v>
+      </c>
+      <c r="D48" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="E48" s="20" t="s">
         <v>317</v>
       </c>
-      <c r="E47" s="20" t="s">
+      <c r="F48" s="20" t="s">
         <v>318</v>
       </c>
-      <c r="F47" s="20" t="s">
+      <c r="G48" s="90" t="s">
+        <v>286</v>
+      </c>
+      <c r="H48" s="90" t="s">
+        <v>5</v>
+      </c>
+      <c r="I48" s="20" t="s">
         <v>319</v>
       </c>
-      <c r="G47" s="90" t="s">
-        <v>287</v>
-      </c>
-      <c r="H47" s="90" t="s">
-        <v>5</v>
-      </c>
-      <c r="I47" s="20" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="91" t="s">
-        <v>186</v>
-      </c>
-      <c r="B48" s="55" t="s">
-        <v>192</v>
-      </c>
-      <c r="C48" s="92" t="s">
-        <v>80</v>
-      </c>
-      <c r="D48" s="91" t="s">
-        <v>321</v>
-      </c>
-      <c r="E48" s="21" t="s">
-        <v>322</v>
-      </c>
-      <c r="F48" s="21" t="s">
-        <v>323</v>
-      </c>
-      <c r="G48" s="93" t="s">
-        <v>324</v>
-      </c>
-      <c r="H48" s="93" t="s">
-        <v>157</v>
-      </c>
-      <c r="I48" s="91" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:9" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="91" t="s">
         <v>186</v>
       </c>
@@ -4082,42 +4062,42 @@
         <v>80</v>
       </c>
       <c r="D49" s="91" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E49" s="21" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="F49" s="21" t="s">
-        <v>327</v>
-      </c>
-      <c r="G49" s="93">
-        <v>2023</v>
+        <v>322</v>
+      </c>
+      <c r="G49" s="93" t="s">
+        <v>323</v>
       </c>
       <c r="H49" s="93" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I49" s="91" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="110.25" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="91" t="s">
         <v>186</v>
       </c>
-      <c r="B50" s="94" t="s">
+      <c r="B50" s="55" t="s">
         <v>192</v>
       </c>
       <c r="C50" s="92" t="s">
         <v>80</v>
       </c>
       <c r="D50" s="91" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="E50" s="21" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="F50" s="21" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="G50" s="93">
         <v>2023</v>
@@ -4126,138 +4106,161 @@
         <v>156</v>
       </c>
       <c r="I50" s="91" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A51" s="21" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A51" s="91" t="s">
         <v>186</v>
       </c>
       <c r="B51" s="94" t="s">
         <v>192</v>
       </c>
-      <c r="C51" s="95" t="s">
+      <c r="C51" s="92" t="s">
         <v>80</v>
       </c>
-      <c r="D51" s="21" t="s">
-        <v>332</v>
+      <c r="D51" s="91" t="s">
+        <v>328</v>
       </c>
       <c r="E51" s="21" t="s">
-        <v>200</v>
+        <v>329</v>
       </c>
       <c r="F51" s="21" t="s">
-        <v>333</v>
-      </c>
-      <c r="G51" s="96" t="s">
-        <v>287</v>
-      </c>
-      <c r="H51" s="96" t="s">
-        <v>5</v>
-      </c>
-      <c r="I51" s="21" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="91" t="s">
+        <v>330</v>
+      </c>
+      <c r="G51" s="93">
+        <v>2023</v>
+      </c>
+      <c r="H51" s="93" t="s">
+        <v>156</v>
+      </c>
+      <c r="I51" s="91" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A52" s="21" t="s">
         <v>186</v>
       </c>
       <c r="B52" s="94" t="s">
         <v>192</v>
       </c>
-      <c r="C52" s="92" t="s">
+      <c r="C52" s="95" t="s">
         <v>80</v>
       </c>
-      <c r="D52" s="91" t="s">
-        <v>334</v>
+      <c r="D52" s="21" t="s">
+        <v>331</v>
       </c>
       <c r="E52" s="21" t="s">
-        <v>318</v>
+        <v>200</v>
       </c>
       <c r="F52" s="21" t="s">
-        <v>335</v>
-      </c>
-      <c r="G52" s="93">
-        <v>2023</v>
-      </c>
-      <c r="H52" s="93" t="s">
-        <v>156</v>
-      </c>
-      <c r="I52" s="91" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="G52" s="96" t="s">
+        <v>286</v>
+      </c>
+      <c r="H52" s="96" t="s">
+        <v>5</v>
+      </c>
+      <c r="I52" s="21" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="91" t="s">
         <v>186</v>
       </c>
       <c r="B53" s="94" t="s">
         <v>192</v>
       </c>
-      <c r="C53" s="95" t="s">
+      <c r="C53" s="92" t="s">
         <v>80</v>
       </c>
-      <c r="D53" s="21" t="s">
-        <v>336</v>
+      <c r="D53" s="91" t="s">
+        <v>333</v>
       </c>
       <c r="E53" s="21" t="s">
-        <v>337</v>
+        <v>317</v>
       </c>
       <c r="F53" s="21" t="s">
-        <v>338</v>
-      </c>
-      <c r="G53" s="96" t="s">
-        <v>287</v>
-      </c>
-      <c r="H53" s="96" t="s">
-        <v>5</v>
-      </c>
-      <c r="I53" s="21" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+        <v>334</v>
+      </c>
+      <c r="G53" s="93">
+        <v>2023</v>
+      </c>
+      <c r="H53" s="93" t="s">
+        <v>156</v>
+      </c>
+      <c r="I53" s="91" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="B54" s="97" t="s">
+      <c r="B54" s="94" t="s">
         <v>192</v>
       </c>
       <c r="C54" s="95" t="s">
         <v>80</v>
       </c>
-      <c r="D54" s="98" t="s">
+      <c r="D54" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="E54" s="21" t="s">
+        <v>336</v>
+      </c>
+      <c r="F54" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="G54" s="96" t="s">
+        <v>286</v>
+      </c>
+      <c r="H54" s="96" t="s">
+        <v>5</v>
+      </c>
+      <c r="I54" s="21" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A55" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="B55" s="97" t="s">
+        <v>192</v>
+      </c>
+      <c r="C55" s="95" t="s">
+        <v>80</v>
+      </c>
+      <c r="D55" s="98" t="s">
+        <v>339</v>
+      </c>
+      <c r="E55" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="F55" s="21" t="s">
         <v>340</v>
       </c>
-      <c r="E54" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="F54" s="21" t="s">
-        <v>341</v>
-      </c>
-      <c r="G54" s="99" t="s">
-        <v>287</v>
-      </c>
-      <c r="H54" s="96" t="s">
-        <v>5</v>
-      </c>
-      <c r="I54" s="21" t="s">
-        <v>314</v>
+      <c r="G55" s="99" t="s">
+        <v>286</v>
+      </c>
+      <c r="H55" s="96" t="s">
+        <v>5</v>
+      </c>
+      <c r="I55" s="21" t="s">
+        <v>313</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I54" xr:uid="{653AF72C-24C0-4E60-8663-786F0182C4B9}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="USA"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A1:A54">
-    <cfRule type="containsText" dxfId="27" priority="1" operator="containsText" text="Associate">
+  <autoFilter ref="A1:I55" xr:uid="{653AF72C-24C0-4E60-8663-786F0182C4B9}"/>
+  <conditionalFormatting sqref="A1:A55">
+    <cfRule type="containsText" dxfId="22" priority="1" operator="containsText" text="Associate">
       <formula>NOT(ISERROR(SEARCH("Associate",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="2" operator="containsText" text="Full">
+    <cfRule type="containsText" dxfId="21" priority="2" operator="containsText" text="Full">
       <formula>NOT(ISERROR(SEARCH("Full",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4276,7 +4279,7 @@
   <sheetData>
     <row r="1" spans="1:13" s="11" customFormat="1" ht="63" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>0</v>
@@ -4466,58 +4469,58 @@
         <v>100</v>
       </c>
       <c r="E1" s="123" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F1" s="123" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G1" s="119" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1" s="118" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="I1" s="26" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J1" s="26" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="K1" s="117" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="L1" s="117" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="N1" s="26" t="s">
         <v>151</v>
       </c>
       <c r="O1" s="117" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P1" s="117" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Q1" s="117" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="R1" s="117" t="s">
         <v>155</v>
       </c>
       <c r="S1" s="117" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="T1" s="117" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="U1" s="117" t="s">
         <v>99</v>
       </c>
       <c r="V1" s="117" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="W1" s="26" t="s">
         <v>2</v>
@@ -4541,49 +4544,49 @@
       </c>
       <c r="F2" s="101"/>
       <c r="G2" s="109" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H2" s="109" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I2" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J2" s="109" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K2" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="L2" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M2" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="N2" s="108" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O2" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="P2" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q2" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="R2" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="S2" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="T2" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="U2" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="V2" s="23" t="s">
         <v>156</v>
@@ -4598,55 +4601,61 @@
         <v>80</v>
       </c>
       <c r="C3" s="109" t="s">
-        <v>123</v>
-      </c>
-      <c r="D3" s="114" t="s">
-        <v>104</v>
-      </c>
-      <c r="E3" s="114" t="s">
-        <v>365</v>
-      </c>
-      <c r="F3" s="114"/>
-      <c r="G3" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="111"/>
-      <c r="J3" s="113"/>
-      <c r="K3" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="L3" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="M3" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="N3" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="O3" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="P3" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q3" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="R3" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="S3" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="T3" s="113" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="101" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3" s="101" t="s">
+        <v>169</v>
+      </c>
+      <c r="F3" s="101" t="s">
+        <v>366</v>
+      </c>
+      <c r="G3" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="H3" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="I3" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="J3" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="K3" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="L3" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="M3" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="N3" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="O3" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="P3" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q3" s="109" t="s">
         <v>349</v>
       </c>
-      <c r="U3" s="113" t="s">
-        <v>5</v>
+      <c r="R3" s="107" t="s">
+        <v>349</v>
+      </c>
+      <c r="S3" s="107" t="s">
+        <v>349</v>
+      </c>
+      <c r="T3" s="107" t="s">
+        <v>371</v>
+      </c>
+      <c r="U3" s="107" t="s">
+        <v>347</v>
       </c>
       <c r="V3" s="23" t="s">
         <v>156</v>
@@ -4655,67 +4664,67 @@
     </row>
     <row r="4" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="109" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B4" s="110" t="s">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C4" s="109" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D4" s="101" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="E4" s="101" t="s">
         <v>169</v>
       </c>
       <c r="F4" s="101" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G4" s="109" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H4" s="109" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I4" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="J4" s="116" t="s">
-        <v>349</v>
+        <v>348</v>
+      </c>
+      <c r="J4" s="109" t="s">
+        <v>348</v>
       </c>
       <c r="K4" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="L4" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M4" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="N4" s="108" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O4" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="P4" s="107" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="Q4" s="107" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="R4" s="107" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="S4" s="107" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="T4" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="U4" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="V4" s="23" t="s">
         <v>156</v>
@@ -4730,61 +4739,61 @@
         <v>80</v>
       </c>
       <c r="C5" s="109" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D5" s="101" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E5" s="101" t="s">
         <v>182</v>
       </c>
       <c r="F5" s="101" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G5" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="H5" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="I5" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="J5" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="K5" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="L5" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="M5" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="N5" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="O5" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="P5" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q5" s="107" t="s">
         <v>349</v>
       </c>
-      <c r="H5" s="109" t="s">
+      <c r="R5" s="107" t="s">
         <v>349</v>
       </c>
-      <c r="I5" s="107" t="s">
+      <c r="S5" s="107" t="s">
         <v>349</v>
       </c>
-      <c r="J5" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="K5" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="L5" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="M5" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="N5" s="108" t="s">
-        <v>349</v>
-      </c>
-      <c r="O5" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="P5" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="Q5" s="107" t="s">
-        <v>350</v>
-      </c>
-      <c r="R5" s="107" t="s">
-        <v>350</v>
-      </c>
-      <c r="S5" s="107" t="s">
-        <v>350</v>
-      </c>
       <c r="T5" s="107" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="U5" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="V5" s="23" t="s">
         <v>156</v>
@@ -4793,72 +4802,72 @@
     </row>
     <row r="6" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="109" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B6" s="110" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="C6" s="109" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D6" s="101" t="s">
-        <v>110</v>
+        <v>17</v>
       </c>
       <c r="E6" s="101" t="s">
         <v>182</v>
       </c>
       <c r="F6" s="101" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G6" s="109" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H6" s="109" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I6" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J6" s="109" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K6" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="L6" s="107" t="s">
         <v>349</v>
       </c>
       <c r="M6" s="107" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="N6" s="108" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="O6" s="107" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="P6" s="107" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="Q6" s="107" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="R6" s="107" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="S6" s="107" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="T6" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="U6" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="V6" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="W6" s="106"/>
+      <c r="W6" s="107"/>
     </row>
     <row r="7" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="109" t="s">
@@ -4868,13 +4877,13 @@
         <v>80</v>
       </c>
       <c r="C7" s="109" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D7" s="114" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E7" s="114" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="F7" s="114"/>
       <c r="G7" s="113" t="s">
@@ -4913,7 +4922,7 @@
         <v>5</v>
       </c>
       <c r="T7" s="113" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="U7" s="113" t="s">
         <v>5</v>
@@ -4925,274 +4934,274 @@
     </row>
     <row r="8" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="109" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B8" s="110" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" s="109" t="s">
-        <v>126</v>
+        <v>21</v>
+      </c>
+      <c r="C8" s="108" t="s">
+        <v>132</v>
       </c>
       <c r="D8" s="101" t="s">
-        <v>113</v>
-      </c>
-      <c r="E8" s="101" t="s">
-        <v>182</v>
-      </c>
-      <c r="F8" s="101" t="s">
-        <v>367</v>
+        <v>116</v>
+      </c>
+      <c r="E8" s="124" t="s">
+        <v>235</v>
+      </c>
+      <c r="F8" s="124" t="s">
+        <v>366</v>
       </c>
       <c r="G8" s="109" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H8" s="109" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I8" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J8" s="109" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K8" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="L8" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M8" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="N8" s="108" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O8" s="107" t="s">
         <v>349</v>
       </c>
       <c r="P8" s="107" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="Q8" s="107" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="R8" s="107" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="S8" s="107" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="T8" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="U8" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="V8" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="W8" s="106"/>
+      <c r="W8" s="107"/>
     </row>
     <row r="9" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="109" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B9" s="110" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="109" t="s">
-        <v>134</v>
+        <v>21</v>
+      </c>
+      <c r="C9" s="108" t="s">
+        <v>132</v>
       </c>
       <c r="D9" s="101" t="s">
-        <v>119</v>
-      </c>
-      <c r="E9" s="101" t="s">
-        <v>169</v>
-      </c>
-      <c r="F9" s="101" t="s">
-        <v>367</v>
-      </c>
-      <c r="G9" s="109" t="s">
+        <v>117</v>
+      </c>
+      <c r="E9" s="124" t="s">
+        <v>238</v>
+      </c>
+      <c r="F9" s="124" t="s">
+        <v>366</v>
+      </c>
+      <c r="G9" s="115" t="s">
+        <v>348</v>
+      </c>
+      <c r="H9" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="I9" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="J9" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="K9" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="L9" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="M9" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="N9" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="O9" s="109" t="s">
         <v>349</v>
       </c>
-      <c r="H9" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="I9" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="J9" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="K9" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="L9" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="M9" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="N9" s="108" t="s">
-        <v>349</v>
-      </c>
-      <c r="O9" s="107" t="s">
-        <v>349</v>
-      </c>
       <c r="P9" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="Q9" s="107" t="s">
-        <v>349</v>
+        <v>347</v>
+      </c>
+      <c r="Q9" s="109" t="s">
+        <v>348</v>
       </c>
       <c r="R9" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="S9" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="T9" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="U9" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="V9" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="W9" s="106"/>
+      <c r="W9" s="107"/>
     </row>
     <row r="10" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="109" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B10" s="110" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C10" s="109" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D10" s="101" t="s">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="E10" s="101" t="s">
         <v>182</v>
       </c>
       <c r="F10" s="101" t="s">
-        <v>367</v>
-      </c>
-      <c r="G10" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="H10" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="I10" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="J10" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="K10" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="L10" s="107" t="s">
-        <v>350</v>
-      </c>
-      <c r="M10" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="N10" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="O10" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="P10" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="Q10" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="R10" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="S10" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="T10" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="U10" s="107" t="s">
-        <v>348</v>
+        <v>366</v>
+      </c>
+      <c r="G10" s="115" t="s">
+        <v>348</v>
+      </c>
+      <c r="H10" s="113" t="s">
+        <v>348</v>
+      </c>
+      <c r="I10" s="111" t="s">
+        <v>348</v>
+      </c>
+      <c r="J10" s="113" t="s">
+        <v>348</v>
+      </c>
+      <c r="K10" s="111" t="s">
+        <v>348</v>
+      </c>
+      <c r="L10" s="111" t="s">
+        <v>348</v>
+      </c>
+      <c r="M10" s="111" t="s">
+        <v>348</v>
+      </c>
+      <c r="N10" s="112" t="s">
+        <v>348</v>
+      </c>
+      <c r="O10" s="111" t="s">
+        <v>348</v>
+      </c>
+      <c r="P10" s="111" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q10" s="111" t="s">
+        <v>348</v>
+      </c>
+      <c r="R10" s="111" t="s">
+        <v>347</v>
+      </c>
+      <c r="S10" s="111" t="s">
+        <v>347</v>
+      </c>
+      <c r="T10" s="111" t="s">
+        <v>371</v>
+      </c>
+      <c r="U10" s="111" t="s">
+        <v>347</v>
       </c>
       <c r="V10" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="W10" s="107"/>
+      <c r="W10" s="106"/>
     </row>
     <row r="11" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="109" t="s">
         <v>132</v>
       </c>
       <c r="B11" s="110" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="108" t="s">
-        <v>132</v>
+        <v>137</v>
+      </c>
+      <c r="C11" s="109" t="s">
+        <v>131</v>
       </c>
       <c r="D11" s="101" t="s">
-        <v>116</v>
-      </c>
-      <c r="E11" s="124" t="s">
-        <v>235</v>
-      </c>
-      <c r="F11" s="124" t="s">
-        <v>367</v>
+        <v>346</v>
+      </c>
+      <c r="E11" s="101" t="s">
+        <v>213</v>
+      </c>
+      <c r="F11" s="101" t="s">
+        <v>366</v>
       </c>
       <c r="G11" s="109" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H11" s="109" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I11" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J11" s="109" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K11" s="107" t="s">
         <v>349</v>
       </c>
       <c r="L11" s="107" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="M11" s="107" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="N11" s="108" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="O11" s="107" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="P11" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q11" s="107" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="R11" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="S11" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="T11" s="107" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="U11" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="V11" s="23" t="s">
         <v>156</v>
@@ -5201,72 +5210,72 @@
     </row>
     <row r="12" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="109" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B12" s="110" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="C12" s="108" t="s">
-        <v>132</v>
-      </c>
-      <c r="D12" s="101" t="s">
-        <v>117</v>
-      </c>
-      <c r="E12" s="124" t="s">
-        <v>238</v>
-      </c>
-      <c r="F12" s="124" t="s">
-        <v>367</v>
-      </c>
-      <c r="G12" s="115" t="s">
+        <v>370</v>
+      </c>
+      <c r="D12" s="124" t="s">
+        <v>369</v>
+      </c>
+      <c r="E12" s="101" t="s">
+        <v>182</v>
+      </c>
+      <c r="F12" s="101" t="s">
+        <v>366</v>
+      </c>
+      <c r="G12" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="H12" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="I12" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="J12" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="K12" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="L12" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="M12" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="N12" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="O12" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="P12" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q12" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="R12" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="S12" s="107" t="s">
         <v>349</v>
       </c>
-      <c r="H12" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="I12" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="J12" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="K12" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="L12" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="M12" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="N12" s="108" t="s">
-        <v>349</v>
-      </c>
-      <c r="O12" s="109" t="s">
-        <v>350</v>
-      </c>
-      <c r="P12" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="Q12" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="R12" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="S12" s="107" t="s">
-        <v>348</v>
-      </c>
       <c r="T12" s="107" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="U12" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="V12" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="W12" s="107"/>
+      <c r="W12" s="106"/>
     </row>
     <row r="13" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="109" t="s">
@@ -5275,62 +5284,62 @@
       <c r="B13" s="110" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="109" t="s">
-        <v>122</v>
+      <c r="C13" s="108" t="s">
+        <v>370</v>
       </c>
       <c r="D13" s="101" t="s">
-        <v>101</v>
+        <v>368</v>
       </c>
       <c r="E13" s="101" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="F13" s="101" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G13" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="H13" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="I13" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="J13" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="K13" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="L13" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="M13" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="N13" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="O13" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="P13" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q13" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="R13" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="S13" s="107" t="s">
         <v>349</v>
       </c>
-      <c r="H13" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="I13" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="J13" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="K13" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="L13" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="M13" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="N13" s="108" t="s">
-        <v>349</v>
-      </c>
-      <c r="O13" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="P13" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="Q13" s="109" t="s">
-        <v>350</v>
-      </c>
-      <c r="R13" s="107" t="s">
-        <v>350</v>
-      </c>
-      <c r="S13" s="107" t="s">
-        <v>350</v>
-      </c>
       <c r="T13" s="107" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="U13" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="V13" s="23" t="s">
         <v>156</v>
@@ -5342,64 +5351,58 @@
         <v>129</v>
       </c>
       <c r="B14" s="110" t="s">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="C14" s="109" t="s">
-        <v>122</v>
-      </c>
-      <c r="D14" s="101" t="s">
-        <v>102</v>
-      </c>
-      <c r="E14" s="101" t="s">
-        <v>182</v>
-      </c>
-      <c r="F14" s="101" t="s">
-        <v>367</v>
-      </c>
-      <c r="G14" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="H14" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="I14" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="J14" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="K14" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="L14" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="M14" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="N14" s="108" t="s">
-        <v>349</v>
-      </c>
-      <c r="O14" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="P14" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="Q14" s="107" t="s">
-        <v>350</v>
-      </c>
-      <c r="R14" s="107" t="s">
-        <v>350</v>
-      </c>
-      <c r="S14" s="107" t="s">
-        <v>350</v>
-      </c>
-      <c r="T14" s="107" t="s">
-        <v>372</v>
-      </c>
-      <c r="U14" s="107" t="s">
-        <v>348</v>
+        <v>124</v>
+      </c>
+      <c r="D14" s="114" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" s="114" t="s">
+        <v>196</v>
+      </c>
+      <c r="F14" s="114"/>
+      <c r="G14" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="111"/>
+      <c r="J14" s="113"/>
+      <c r="K14" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="113" t="s">
+        <v>5</v>
       </c>
       <c r="V14" s="23" t="s">
         <v>156</v>
@@ -5411,64 +5414,58 @@
         <v>129</v>
       </c>
       <c r="B15" s="110" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" s="108" t="s">
-        <v>371</v>
-      </c>
-      <c r="D15" s="124" t="s">
-        <v>370</v>
-      </c>
-      <c r="E15" s="101" t="s">
-        <v>182</v>
-      </c>
-      <c r="F15" s="101" t="s">
-        <v>367</v>
-      </c>
-      <c r="G15" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="H15" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="I15" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="J15" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="K15" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="L15" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="M15" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="N15" s="108" t="s">
-        <v>349</v>
-      </c>
-      <c r="O15" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="P15" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="Q15" s="107" t="s">
-        <v>350</v>
-      </c>
-      <c r="R15" s="107" t="s">
-        <v>350</v>
-      </c>
-      <c r="S15" s="107" t="s">
-        <v>350</v>
-      </c>
-      <c r="T15" s="107" t="s">
-        <v>372</v>
-      </c>
-      <c r="U15" s="107" t="s">
-        <v>348</v>
+        <v>8</v>
+      </c>
+      <c r="C15" s="109" t="s">
+        <v>124</v>
+      </c>
+      <c r="D15" s="114" t="s">
+        <v>105</v>
+      </c>
+      <c r="E15" s="114" t="s">
+        <v>200</v>
+      </c>
+      <c r="F15" s="114"/>
+      <c r="G15" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="H15" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="I15" s="111"/>
+      <c r="J15" s="113"/>
+      <c r="K15" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="L15" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="M15" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="N15" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="O15" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="P15" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="S15" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="T15" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="U15" s="113" t="s">
+        <v>5</v>
       </c>
       <c r="V15" s="23" t="s">
         <v>156</v>
@@ -5482,62 +5479,56 @@
       <c r="B16" s="110" t="s">
         <v>80</v>
       </c>
-      <c r="C16" s="108" t="s">
-        <v>371</v>
-      </c>
-      <c r="D16" s="101" t="s">
-        <v>369</v>
-      </c>
-      <c r="E16" s="101" t="s">
-        <v>182</v>
-      </c>
-      <c r="F16" s="101" t="s">
-        <v>367</v>
-      </c>
-      <c r="G16" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="H16" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="I16" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="J16" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="K16" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="L16" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="M16" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="N16" s="108" t="s">
-        <v>349</v>
-      </c>
-      <c r="O16" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="P16" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="Q16" s="107" t="s">
-        <v>350</v>
-      </c>
-      <c r="R16" s="107" t="s">
-        <v>350</v>
-      </c>
-      <c r="S16" s="107" t="s">
-        <v>350</v>
-      </c>
-      <c r="T16" s="107" t="s">
-        <v>372</v>
-      </c>
-      <c r="U16" s="107" t="s">
-        <v>348</v>
+      <c r="C16" s="109" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="114" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" s="114" t="s">
+        <v>317</v>
+      </c>
+      <c r="F16" s="114"/>
+      <c r="G16" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="H16" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="I16" s="111"/>
+      <c r="J16" s="113"/>
+      <c r="K16" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="L16" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="M16" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="N16" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="O16" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="P16" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q16" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="R16" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="S16" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="T16" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="U16" s="113" t="s">
+        <v>5</v>
       </c>
       <c r="V16" s="23" t="s">
         <v>156</v>
@@ -5555,58 +5546,58 @@
         <v>125</v>
       </c>
       <c r="D17" s="101" t="s">
-        <v>28</v>
+        <v>107</v>
       </c>
       <c r="E17" s="101" t="s">
         <v>169</v>
       </c>
       <c r="F17" s="101" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G17" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="H17" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="I17" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="J17" s="116" t="s">
+        <v>348</v>
+      </c>
+      <c r="K17" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="L17" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="M17" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="N17" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="O17" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="P17" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q17" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="R17" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="S17" s="107" t="s">
         <v>349</v>
       </c>
-      <c r="H17" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="I17" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="J17" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="K17" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="L17" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="M17" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="N17" s="108" t="s">
-        <v>349</v>
-      </c>
-      <c r="O17" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="P17" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="Q17" s="107" t="s">
-        <v>350</v>
-      </c>
-      <c r="R17" s="107" t="s">
-        <v>350</v>
-      </c>
-      <c r="S17" s="107" t="s">
-        <v>350</v>
-      </c>
       <c r="T17" s="107" t="s">
-        <v>372</v>
+        <v>348</v>
       </c>
       <c r="U17" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="V17" s="23" t="s">
         <v>156</v>
@@ -5627,53 +5618,53 @@
         <v>108</v>
       </c>
       <c r="E18" s="101" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F18" s="101"/>
       <c r="G18" s="109" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H18" s="109" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I18" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J18" s="109" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K18" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="L18" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M18" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="N18" s="108" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O18" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="P18" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q18" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="R18" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="S18" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="T18" s="107" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="U18" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="V18" s="23" t="s">
         <v>156</v>
@@ -5688,130 +5679,124 @@
         <v>80</v>
       </c>
       <c r="C19" s="109" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D19" s="101" t="s">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="E19" s="101" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="F19" s="101" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G19" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="H19" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="I19" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="J19" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="K19" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="L19" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="M19" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="N19" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="O19" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="P19" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q19" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="R19" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="S19" s="107" t="s">
         <v>349</v>
       </c>
-      <c r="H19" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="I19" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="J19" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="K19" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="L19" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="M19" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="N19" s="108" t="s">
-        <v>349</v>
-      </c>
-      <c r="O19" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="P19" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="Q19" s="107" t="s">
-        <v>350</v>
-      </c>
-      <c r="R19" s="107" t="s">
-        <v>350</v>
-      </c>
-      <c r="S19" s="107" t="s">
-        <v>350</v>
-      </c>
       <c r="T19" s="107" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="U19" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="V19" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="W19" s="107"/>
+      <c r="W19" s="106"/>
     </row>
     <row r="20" spans="1:23" s="103" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="109" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="B20" s="110" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="C20" s="109" t="s">
-        <v>133</v>
-      </c>
-      <c r="D20" s="101" t="s">
-        <v>118</v>
-      </c>
-      <c r="E20" s="101" t="s">
-        <v>182</v>
-      </c>
-      <c r="F20" s="101" t="s">
-        <v>367</v>
-      </c>
-      <c r="G20" s="115" t="s">
-        <v>349</v>
+        <v>126</v>
+      </c>
+      <c r="D20" s="114" t="s">
+        <v>112</v>
+      </c>
+      <c r="E20" s="114" t="s">
+        <v>329</v>
+      </c>
+      <c r="F20" s="114"/>
+      <c r="G20" s="113" t="s">
+        <v>5</v>
       </c>
       <c r="H20" s="113" t="s">
-        <v>349</v>
-      </c>
-      <c r="I20" s="111" t="s">
-        <v>349</v>
-      </c>
-      <c r="J20" s="113" t="s">
-        <v>349</v>
-      </c>
-      <c r="K20" s="111" t="s">
-        <v>349</v>
-      </c>
-      <c r="L20" s="111" t="s">
-        <v>349</v>
-      </c>
-      <c r="M20" s="111" t="s">
-        <v>349</v>
-      </c>
-      <c r="N20" s="112" t="s">
-        <v>349</v>
-      </c>
-      <c r="O20" s="111" t="s">
-        <v>349</v>
-      </c>
-      <c r="P20" s="111" t="s">
-        <v>348</v>
-      </c>
-      <c r="Q20" s="111" t="s">
-        <v>349</v>
-      </c>
-      <c r="R20" s="111" t="s">
-        <v>348</v>
-      </c>
-      <c r="S20" s="111" t="s">
-        <v>348</v>
-      </c>
-      <c r="T20" s="111" t="s">
-        <v>372</v>
-      </c>
-      <c r="U20" s="111" t="s">
-        <v>348</v>
+        <v>5</v>
+      </c>
+      <c r="I20" s="111"/>
+      <c r="J20" s="113"/>
+      <c r="K20" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="O20" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="S20" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="T20" s="113" t="s">
+        <v>348</v>
+      </c>
+      <c r="U20" s="113" t="s">
+        <v>5</v>
       </c>
       <c r="V20" s="23" t="s">
         <v>156</v>
@@ -5836,49 +5821,49 @@
       </c>
       <c r="F21" s="101"/>
       <c r="G21" s="109" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H21" s="109" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I21" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J21" s="109" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K21" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="L21" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M21" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="N21" s="108" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O21" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="P21" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q21" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="R21" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="S21" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="T21" s="107" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="U21" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="V21" s="23" t="s">
         <v>156</v>
@@ -5887,130 +5872,136 @@
     </row>
     <row r="22" spans="1:23" s="103" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="109" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B22" s="110" t="s">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="C22" s="109" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D22" s="101" t="s">
-        <v>347</v>
+        <v>109</v>
       </c>
       <c r="E22" s="101" t="s">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="F22" s="101" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G22" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="H22" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="I22" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="J22" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="K22" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="L22" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="M22" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="N22" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="O22" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="P22" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q22" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="R22" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="S22" s="107" t="s">
         <v>349</v>
       </c>
-      <c r="H22" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="I22" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="J22" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="K22" s="107" t="s">
-        <v>350</v>
-      </c>
-      <c r="L22" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="M22" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="N22" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="O22" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="P22" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="Q22" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="R22" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="S22" s="107" t="s">
-        <v>348</v>
-      </c>
       <c r="T22" s="107" t="s">
-        <v>372</v>
+        <v>348</v>
       </c>
       <c r="U22" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="V22" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="W22" s="107"/>
+      <c r="W22" s="106"/>
     </row>
     <row r="23" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="109" t="s">
         <v>129</v>
       </c>
       <c r="B23" s="110" t="s">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="C23" s="109" t="s">
-        <v>124</v>
-      </c>
-      <c r="D23" s="114" t="s">
-        <v>106</v>
-      </c>
-      <c r="E23" s="114" t="s">
-        <v>196</v>
-      </c>
-      <c r="F23" s="114"/>
-      <c r="G23" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="H23" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="I23" s="111"/>
-      <c r="J23" s="113"/>
-      <c r="K23" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="L23" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="M23" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="N23" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="O23" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="P23" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q23" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="R23" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="S23" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="T23" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="U23" s="113" t="s">
-        <v>5</v>
+        <v>126</v>
+      </c>
+      <c r="D23" s="101" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" s="101" t="s">
+        <v>182</v>
+      </c>
+      <c r="F23" s="101" t="s">
+        <v>366</v>
+      </c>
+      <c r="G23" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="H23" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="I23" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="J23" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="K23" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="L23" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="M23" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="N23" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="O23" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="P23" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q23" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="R23" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="S23" s="107" t="s">
+        <v>349</v>
+      </c>
+      <c r="T23" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="U23" s="107" t="s">
+        <v>347</v>
       </c>
       <c r="V23" s="23" t="s">
         <v>156</v>
@@ -6022,58 +6013,64 @@
         <v>129</v>
       </c>
       <c r="B24" s="110" t="s">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="C24" s="109" t="s">
-        <v>124</v>
-      </c>
-      <c r="D24" s="114" t="s">
-        <v>105</v>
-      </c>
-      <c r="E24" s="114" t="s">
-        <v>200</v>
-      </c>
-      <c r="F24" s="114"/>
-      <c r="G24" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="H24" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="I24" s="111"/>
-      <c r="J24" s="113"/>
-      <c r="K24" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="L24" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="M24" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="N24" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="O24" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="P24" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q24" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="R24" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="S24" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="T24" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="U24" s="113" t="s">
-        <v>5</v>
+        <v>126</v>
+      </c>
+      <c r="D24" s="101" t="s">
+        <v>113</v>
+      </c>
+      <c r="E24" s="101" t="s">
+        <v>182</v>
+      </c>
+      <c r="F24" s="101" t="s">
+        <v>366</v>
+      </c>
+      <c r="G24" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="H24" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="I24" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="J24" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="K24" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="L24" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="M24" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="N24" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="O24" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="P24" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q24" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="R24" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="S24" s="107" t="s">
+        <v>349</v>
+      </c>
+      <c r="T24" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="U24" s="107" t="s">
+        <v>347</v>
       </c>
       <c r="V24" s="23" t="s">
         <v>156</v>
@@ -6088,13 +6085,13 @@
         <v>80</v>
       </c>
       <c r="C25" s="109" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D25" s="114" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E25" s="114" t="s">
-        <v>318</v>
+        <v>365</v>
       </c>
       <c r="F25" s="114"/>
       <c r="G25" s="113" t="s">
@@ -6148,31 +6145,33 @@
         <v>129</v>
       </c>
       <c r="B26" s="110" t="s">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="C26" s="109" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D26" s="114" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E26" s="114" t="s">
+        <v>182</v>
+      </c>
+      <c r="F26" s="114" t="s">
         <v>366</v>
       </c>
-      <c r="F26" s="114"/>
       <c r="G26" s="113" t="s">
-        <v>5</v>
+        <v>348</v>
       </c>
       <c r="H26" s="113" t="s">
-        <v>5</v>
+        <v>348</v>
       </c>
       <c r="I26" s="111"/>
       <c r="J26" s="113"/>
       <c r="K26" s="113" t="s">
-        <v>5</v>
+        <v>348</v>
       </c>
       <c r="L26" s="113" t="s">
-        <v>5</v>
+        <v>348</v>
       </c>
       <c r="M26" s="113" t="s">
         <v>5</v>
@@ -6181,16 +6180,16 @@
         <v>5</v>
       </c>
       <c r="O26" s="113" t="s">
-        <v>5</v>
+        <v>348</v>
       </c>
       <c r="P26" s="113" t="s">
-        <v>5</v>
+        <v>348</v>
       </c>
       <c r="Q26" s="113" t="s">
-        <v>5</v>
+        <v>348</v>
       </c>
       <c r="R26" s="113" t="s">
-        <v>5</v>
+        <v>348</v>
       </c>
       <c r="S26" s="113" t="s">
         <v>5</v>
@@ -6204,97 +6203,99 @@
       <c r="V26" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="W26" s="106"/>
+      <c r="W26" s="106" t="s">
+        <v>345</v>
+      </c>
     </row>
     <row r="27" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="109" t="s">
         <v>129</v>
       </c>
       <c r="B27" s="110" t="s">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="C27" s="109" t="s">
-        <v>127</v>
-      </c>
-      <c r="D27" s="114" t="s">
-        <v>114</v>
-      </c>
-      <c r="E27" s="114" t="s">
+        <v>129</v>
+      </c>
+      <c r="D27" s="101" t="s">
+        <v>115</v>
+      </c>
+      <c r="E27" s="101" t="s">
         <v>182</v>
       </c>
-      <c r="F27" s="114" t="s">
-        <v>367</v>
-      </c>
-      <c r="G27" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="H27" s="113" t="s">
-        <v>346</v>
-      </c>
-      <c r="I27" s="111"/>
-      <c r="J27" s="113"/>
-      <c r="K27" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="L27" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="M27" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="N27" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="O27" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="P27" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q27" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="R27" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="S27" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="T27" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="U27" s="113" t="s">
-        <v>5</v>
+      <c r="F27" s="101" t="s">
+        <v>366</v>
+      </c>
+      <c r="G27" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="H27" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="I27" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="J27" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="K27" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="L27" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="M27" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="N27" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="O27" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="P27" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q27" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="R27" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="S27" s="107" t="s">
+        <v>349</v>
+      </c>
+      <c r="T27" s="107" t="s">
+        <v>371</v>
+      </c>
+      <c r="U27" s="107" t="s">
+        <v>347</v>
       </c>
       <c r="V27" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="W27" s="106"/>
+      <c r="W27" s="107"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W27" xr:uid="{ED25CF60-E519-46A5-8820-1361CFDEEEDA}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:W27">
-      <sortCondition ref="T1:T27"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:W27" xr:uid="{ED25CF60-E519-46A5-8820-1361CFDEEEDA}"/>
   <conditionalFormatting sqref="G2:U27">
-    <cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="Imputation">
+    <cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="Planned">
+      <formula>NOT(ISERROR(SEARCH("Planned",G2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="19" priority="2" operator="containsText" text="Imputation">
       <formula>NOT(ISERROR(SEARCH("Imputation",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="Not Applicable">
+    <cfRule type="containsText" dxfId="18" priority="3" operator="containsText" text="Not Applicable">
       <formula>NOT(ISERROR(SEARCH("Not Applicable",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="Completed">
+    <cfRule type="containsText" dxfId="17" priority="4" operator="containsText" text="Completed">
       <formula>NOT(ISERROR(SEARCH("Completed",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="Ongoing">
+    <cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="Ongoing">
       <formula>NOT(ISERROR(SEARCH("Ongoing",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="6" operator="containsText" text="Not started">
+    <cfRule type="containsText" dxfId="15" priority="6" operator="containsText" text="Not started">
       <formula>NOT(ISERROR(SEARCH("Not started",G2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="Planned">
-      <formula>NOT(ISERROR(SEARCH("Planned",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
@@ -6337,7 +6338,7 @@
         <v>100</v>
       </c>
       <c r="D1" s="100" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E1" s="100" t="s">
         <v>149</v>
@@ -6378,25 +6379,25 @@
         <v>156</v>
       </c>
       <c r="E2" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F2" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G2" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H2" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I2" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J2" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K2" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L2" s="27"/>
     </row>
@@ -6414,25 +6415,25 @@
         <v>156</v>
       </c>
       <c r="E3" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F3" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G3" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H3" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I3" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J3" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K3" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L3" s="27"/>
     </row>
@@ -6450,25 +6451,25 @@
         <v>156</v>
       </c>
       <c r="E4" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F4" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G4" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H4" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I4" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J4" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K4" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L4" s="27"/>
     </row>
@@ -6486,25 +6487,25 @@
         <v>156</v>
       </c>
       <c r="E5" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F5" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G5" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H5" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I5" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J5" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K5" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L5" s="27"/>
     </row>
@@ -6522,25 +6523,25 @@
         <v>156</v>
       </c>
       <c r="E6" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F6" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G6" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H6" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I6" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J6" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K6" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L6" s="27"/>
     </row>
@@ -6558,25 +6559,25 @@
         <v>156</v>
       </c>
       <c r="E7" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F7" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G7" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H7" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I7" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J7" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K7" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L7" s="27"/>
     </row>
@@ -6594,25 +6595,25 @@
         <v>156</v>
       </c>
       <c r="E8" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F8" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G8" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H8" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I8" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J8" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K8" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L8" s="27"/>
     </row>
@@ -6630,25 +6631,25 @@
         <v>156</v>
       </c>
       <c r="E9" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F9" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G9" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H9" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I9" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J9" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K9" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L9" s="27"/>
     </row>
@@ -6666,25 +6667,25 @@
         <v>156</v>
       </c>
       <c r="E10" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F10" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G10" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H10" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I10" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J10" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K10" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L10" s="27"/>
     </row>
@@ -6702,25 +6703,25 @@
         <v>156</v>
       </c>
       <c r="E11" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F11" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G11" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H11" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I11" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J11" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K11" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L11" s="27"/>
     </row>
@@ -6738,25 +6739,25 @@
         <v>156</v>
       </c>
       <c r="E12" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F12" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G12" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H12" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I12" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J12" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K12" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L12" s="27"/>
     </row>
@@ -6774,25 +6775,25 @@
         <v>156</v>
       </c>
       <c r="E13" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F13" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G13" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H13" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I13" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J13" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K13" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L13" s="27"/>
     </row>
@@ -6810,25 +6811,25 @@
         <v>156</v>
       </c>
       <c r="E14" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F14" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G14" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H14" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I14" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J14" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K14" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L14" s="27"/>
     </row>
@@ -6846,25 +6847,25 @@
         <v>156</v>
       </c>
       <c r="E15" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F15" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G15" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H15" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I15" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J15" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K15" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L15" s="27"/>
     </row>
@@ -6882,25 +6883,25 @@
         <v>156</v>
       </c>
       <c r="E16" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F16" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G16" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H16" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I16" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J16" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K16" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L16" s="27"/>
     </row>
@@ -6918,25 +6919,25 @@
         <v>156</v>
       </c>
       <c r="E17" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F17" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G17" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H17" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I17" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J17" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K17" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L17" s="27"/>
     </row>
@@ -6954,25 +6955,25 @@
         <v>156</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F18" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G18" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H18" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I18" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J18" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K18" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L18" s="27"/>
     </row>
@@ -6990,25 +6991,25 @@
         <v>156</v>
       </c>
       <c r="E19" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F19" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G19" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H19" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I19" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J19" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K19" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L19" s="27"/>
     </row>
@@ -7026,25 +7027,25 @@
         <v>156</v>
       </c>
       <c r="E20" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F20" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G20" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H20" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I20" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J20" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K20" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L20" s="27"/>
     </row>
@@ -7062,25 +7063,25 @@
         <v>156</v>
       </c>
       <c r="E21" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F21" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G21" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H21" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I21" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J21" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K21" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L21" s="27"/>
     </row>
@@ -7098,25 +7099,25 @@
         <v>156</v>
       </c>
       <c r="E22" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F22" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G22" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H22" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I22" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J22" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K22" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L22" s="27"/>
     </row>
@@ -7134,25 +7135,25 @@
         <v>156</v>
       </c>
       <c r="E23" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F23" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G23" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H23" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I23" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J23" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K23" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L23" s="27"/>
     </row>
@@ -7170,25 +7171,25 @@
         <v>156</v>
       </c>
       <c r="E24" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F24" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G24" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H24" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I24" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J24" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K24" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L24" s="27"/>
     </row>
@@ -7206,25 +7207,25 @@
         <v>156</v>
       </c>
       <c r="E25" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F25" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G25" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H25" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I25" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J25" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K25" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L25" s="27"/>
     </row>
@@ -7242,44 +7243,44 @@
         <v>156</v>
       </c>
       <c r="E26" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F26" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G26" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H26" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I26" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J26" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K26" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L26" s="31"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L26" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <conditionalFormatting sqref="E2:K26">
-    <cfRule type="containsText" dxfId="25" priority="1" operator="containsText" text="Imputation">
+    <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="Imputation">
       <formula>NOT(ISERROR(SEARCH("Imputation",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="2" operator="containsText" text="Not Applicable">
+    <cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="Not Applicable">
       <formula>NOT(ISERROR(SEARCH("Not Applicable",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="23" priority="3" operator="containsText" text="Completed">
+    <cfRule type="containsText" dxfId="12" priority="3" operator="containsText" text="Completed">
       <formula>NOT(ISERROR(SEARCH("Completed",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="4" operator="containsText" text="Ongoing">
+    <cfRule type="containsText" dxfId="11" priority="4" operator="containsText" text="Ongoing">
       <formula>NOT(ISERROR(SEARCH("Ongoing",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="5" operator="containsText" text="Not started">
+    <cfRule type="containsText" dxfId="10" priority="5" operator="containsText" text="Not started">
       <formula>NOT(ISERROR(SEARCH("Not started",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7356,25 +7357,25 @@
         <v>156</v>
       </c>
       <c r="E2" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F2" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G2" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H2" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I2" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J2" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K2" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L2" s="31"/>
     </row>
@@ -7392,25 +7393,25 @@
         <v>156</v>
       </c>
       <c r="E3" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F3" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G3" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H3" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I3" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J3" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K3" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L3" s="31"/>
     </row>
@@ -7428,25 +7429,25 @@
         <v>156</v>
       </c>
       <c r="E4" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F4" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G4" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H4" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I4" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J4" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K4" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L4" s="31"/>
     </row>
@@ -7464,25 +7465,25 @@
         <v>156</v>
       </c>
       <c r="E5" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F5" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G5" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H5" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I5" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J5" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K5" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L5" s="31"/>
     </row>
@@ -7500,25 +7501,25 @@
         <v>156</v>
       </c>
       <c r="E6" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F6" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G6" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H6" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I6" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J6" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K6" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L6" s="31"/>
     </row>
@@ -7536,25 +7537,25 @@
         <v>156</v>
       </c>
       <c r="E7" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F7" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G7" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H7" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I7" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J7" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K7" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L7" s="31"/>
     </row>
@@ -7572,25 +7573,25 @@
         <v>156</v>
       </c>
       <c r="E8" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F8" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G8" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H8" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I8" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J8" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K8" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L8" s="31"/>
     </row>
@@ -7608,25 +7609,25 @@
         <v>156</v>
       </c>
       <c r="E9" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F9" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G9" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H9" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I9" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J9" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K9" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L9" s="31"/>
     </row>
@@ -7644,25 +7645,25 @@
         <v>156</v>
       </c>
       <c r="E10" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F10" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G10" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H10" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I10" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J10" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K10" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L10" s="31"/>
     </row>
@@ -7680,25 +7681,25 @@
         <v>156</v>
       </c>
       <c r="E11" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F11" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G11" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H11" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I11" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J11" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K11" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L11" s="31"/>
     </row>
@@ -7716,25 +7717,25 @@
         <v>156</v>
       </c>
       <c r="E12" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F12" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G12" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H12" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I12" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J12" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K12" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L12" s="31"/>
     </row>
@@ -7752,25 +7753,25 @@
         <v>156</v>
       </c>
       <c r="E13" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F13" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G13" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H13" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I13" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J13" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K13" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L13" s="31"/>
     </row>
@@ -7788,25 +7789,25 @@
         <v>156</v>
       </c>
       <c r="E14" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F14" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G14" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H14" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I14" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J14" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K14" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L14" s="31"/>
     </row>
@@ -7824,25 +7825,25 @@
         <v>156</v>
       </c>
       <c r="E15" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F15" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G15" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H15" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I15" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J15" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K15" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L15" s="31"/>
     </row>
@@ -7860,25 +7861,25 @@
         <v>156</v>
       </c>
       <c r="E16" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F16" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G16" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H16" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I16" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J16" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K16" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L16" s="31"/>
     </row>
@@ -7896,25 +7897,25 @@
         <v>156</v>
       </c>
       <c r="E17" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F17" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G17" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H17" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I17" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J17" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K17" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L17" s="31"/>
     </row>
@@ -7932,25 +7933,25 @@
         <v>156</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F18" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G18" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H18" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I18" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J18" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K18" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L18" s="31"/>
     </row>
@@ -7968,25 +7969,25 @@
         <v>156</v>
       </c>
       <c r="E19" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F19" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G19" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H19" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I19" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J19" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K19" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L19" s="31"/>
     </row>
@@ -8004,25 +8005,25 @@
         <v>156</v>
       </c>
       <c r="E20" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F20" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G20" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H20" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I20" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J20" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K20" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L20" s="31"/>
     </row>
@@ -8040,25 +8041,25 @@
         <v>156</v>
       </c>
       <c r="E21" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F21" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G21" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H21" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I21" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J21" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K21" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L21" s="31"/>
     </row>
@@ -8076,25 +8077,25 @@
         <v>156</v>
       </c>
       <c r="E22" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F22" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G22" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H22" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I22" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J22" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K22" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L22" s="31"/>
     </row>
@@ -8112,25 +8113,25 @@
         <v>156</v>
       </c>
       <c r="E23" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F23" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G23" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H23" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I23" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J23" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K23" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L23" s="31"/>
     </row>
@@ -8148,25 +8149,25 @@
         <v>156</v>
       </c>
       <c r="E24" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F24" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G24" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H24" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I24" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J24" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K24" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L24" s="31"/>
     </row>
@@ -8184,25 +8185,25 @@
         <v>156</v>
       </c>
       <c r="E25" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F25" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G25" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H25" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I25" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J25" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K25" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L25" s="31"/>
     </row>
@@ -8220,43 +8221,43 @@
         <v>156</v>
       </c>
       <c r="E26" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F26" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G26" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H26" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I26" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J26" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K26" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L26" s="31"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:K26">
-    <cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="Imputation">
+    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="Imputation">
       <formula>NOT(ISERROR(SEARCH("Imputation",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="2" operator="containsText" text="Not Applicable">
+    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="Not Applicable">
       <formula>NOT(ISERROR(SEARCH("Not Applicable",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="3" operator="containsText" text="Completed">
+    <cfRule type="containsText" dxfId="7" priority="3" operator="containsText" text="Completed">
       <formula>NOT(ISERROR(SEARCH("Completed",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="4" operator="containsText" text="Ongoing">
+    <cfRule type="containsText" dxfId="6" priority="4" operator="containsText" text="Ongoing">
       <formula>NOT(ISERROR(SEARCH("Ongoing",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="Not started">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="Not started">
       <formula>NOT(ISERROR(SEARCH("Not started",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8271,7 +8272,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -8301,7 +8302,7 @@
         <v>63</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>64</v>
@@ -8369,7 +8370,7 @@
         <v>53</v>
       </c>
       <c r="I3" s="120" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J3" s="4"/>
     </row>
@@ -8459,7 +8460,7 @@
         <v>53</v>
       </c>
       <c r="I6" s="120" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J6" s="4"/>
     </row>
@@ -8480,7 +8481,7 @@
         <v>53</v>
       </c>
       <c r="F7" s="120" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G7" s="120" t="s">
         <v>148</v>
@@ -8519,7 +8520,7 @@
         <v>53</v>
       </c>
       <c r="I8" s="120" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J8" s="4"/>
     </row>
@@ -8579,7 +8580,7 @@
         <v>53</v>
       </c>
       <c r="I10" s="120" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J10" s="4"/>
     </row>
@@ -8609,7 +8610,7 @@
         <v>53</v>
       </c>
       <c r="I11" s="120" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J11" s="4"/>
     </row>
@@ -8624,13 +8625,13 @@
         <v>53</v>
       </c>
       <c r="D12" s="120" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E12" s="120" t="s">
         <v>54</v>
       </c>
       <c r="F12" s="120" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G12" s="120" t="s">
         <v>148</v>
@@ -8639,7 +8640,7 @@
         <v>53</v>
       </c>
       <c r="I12" s="120" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J12" s="4"/>
     </row>
@@ -8660,16 +8661,16 @@
         <v>54</v>
       </c>
       <c r="F13" s="120" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G13" s="120" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H13" s="120" t="s">
         <v>53</v>
       </c>
       <c r="I13" s="120" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -8721,7 +8722,7 @@
         <v>54</v>
       </c>
       <c r="F15" s="120" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G15" s="120" t="s">
         <v>148</v>
@@ -8730,7 +8731,7 @@
         <v>53</v>
       </c>
       <c r="I15" s="120" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>20</v>
@@ -8882,7 +8883,7 @@
         <v>53</v>
       </c>
       <c r="I20" s="120" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J20" s="4"/>
     </row>
@@ -9007,72 +9008,71 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>35</v>
+        <v>375</v>
       </c>
       <c r="C25" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="D25" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="E25" s="120" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="F25" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="G25" s="120" t="s">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="H25" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="I25" s="120" t="s">
-        <v>53</v>
-      </c>
-      <c r="J25" s="4"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C26" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D26" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="E26" s="120" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="F26" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="G26" s="120" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="H26" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="I26" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C27" s="120" t="s">
         <v>5</v>
@@ -9094,186 +9094,188 @@
       </c>
       <c r="I27" s="120" t="s">
         <v>5</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C28" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="D28" s="120" t="s">
-        <v>362</v>
+        <v>5</v>
       </c>
       <c r="E28" s="120" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="F28" s="120" t="s">
-        <v>362</v>
+        <v>5</v>
       </c>
       <c r="G28" s="120" t="s">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="H28" s="120" t="s">
-        <v>362</v>
+        <v>5</v>
       </c>
       <c r="I28" s="120" t="s">
-        <v>362</v>
-      </c>
-      <c r="J28" s="4"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C29" s="120" t="s">
+        <v>53</v>
+      </c>
+      <c r="D29" s="120" t="s">
+        <v>361</v>
+      </c>
+      <c r="E29" s="120" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="120" t="s">
-        <v>148</v>
-      </c>
-      <c r="E29" s="120" t="s">
-        <v>148</v>
-      </c>
       <c r="F29" s="120" t="s">
-        <v>148</v>
+        <v>361</v>
       </c>
       <c r="G29" s="120" t="s">
         <v>148</v>
       </c>
       <c r="H29" s="120" t="s">
-        <v>148</v>
+        <v>361</v>
       </c>
       <c r="I29" s="120" t="s">
-        <v>148</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="J29" s="4"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" s="120" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="D30" s="120" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="E30" s="120" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="F30" s="120" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="G30" s="120" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="H30" s="120" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="I30" s="120" t="s">
-        <v>5</v>
-      </c>
-      <c r="J30" s="4"/>
+        <v>148</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>137</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="C31" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="D31" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="E31" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="F31" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="G31" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="H31" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="I31" s="120" t="s">
-        <v>53</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="J31" s="4"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>137</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C32" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D32" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="E32" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="F32" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="G32" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="H32" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="I32" s="120" t="s">
-        <v>5</v>
-      </c>
-      <c r="J32" s="4"/>
+        <v>53</v>
+      </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="C33" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="D33" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="E33" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="F33" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="G33" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="H33" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="I33" s="120" t="s">
-        <v>362</v>
+        <v>5</v>
       </c>
       <c r="J33" s="4"/>
     </row>
@@ -9282,90 +9284,90 @@
         <v>80</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="C34" s="120" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D34" s="120" t="s">
-        <v>148</v>
+        <v>53</v>
       </c>
       <c r="E34" s="120" t="s">
-        <v>148</v>
+        <v>53</v>
       </c>
       <c r="F34" s="120" t="s">
-        <v>148</v>
+        <v>53</v>
       </c>
       <c r="G34" s="120" t="s">
-        <v>148</v>
+        <v>53</v>
       </c>
       <c r="H34" s="120" t="s">
-        <v>148</v>
+        <v>53</v>
       </c>
       <c r="I34" s="120" t="s">
-        <v>148</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="J34" s="4"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>80</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C35" s="120" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="D35" s="120" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="E35" s="120" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="F35" s="120" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="G35" s="120" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="H35" s="120" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="I35" s="120" t="s">
-        <v>5</v>
-      </c>
-      <c r="J35" s="4"/>
+        <v>148</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>80</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C36" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="D36" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="E36" s="120" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="F36" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="G36" s="120" t="s">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="H36" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="I36" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="J36" s="4"/>
     </row>
@@ -9374,7 +9376,7 @@
         <v>80</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C37" s="120" t="s">
         <v>53</v>
@@ -9404,7 +9406,7 @@
         <v>80</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C38" s="120" t="s">
         <v>53</v>
@@ -9434,7 +9436,7 @@
         <v>80</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C39" s="120" t="s">
         <v>53</v>
@@ -9464,7 +9466,7 @@
         <v>80</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C40" s="120" t="s">
         <v>53</v>
@@ -9487,13 +9489,14 @@
       <c r="I40" s="120" t="s">
         <v>53</v>
       </c>
+      <c r="J40" s="4"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>80</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C41" s="120" t="s">
         <v>53</v>
@@ -9522,28 +9525,28 @@
         <v>80</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C42" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D42" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="E42" s="120" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="F42" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="G42" s="120" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="H42" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="I42" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -9551,28 +9554,28 @@
         <v>80</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C43" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="D43" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="E43" s="120" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="F43" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="G43" s="120" t="s">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="H43" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="I43" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -9580,7 +9583,7 @@
         <v>80</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C44" s="120" t="s">
         <v>53</v>
@@ -9609,28 +9612,28 @@
         <v>80</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="C45" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D45" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="E45" s="120" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="F45" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="G45" s="120" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="H45" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="I45" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -9638,28 +9641,28 @@
         <v>80</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="C46" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="D46" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="E46" s="120" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="F46" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="G46" s="120" t="s">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="H46" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="I46" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -9667,28 +9670,28 @@
         <v>80</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C47" s="120" t="s">
         <v>53</v>
       </c>
       <c r="D47" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="E47" s="120" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="F47" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="G47" s="120" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="H47" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="I47" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -9696,28 +9699,28 @@
         <v>80</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C48" s="120" t="s">
         <v>53</v>
       </c>
       <c r="D48" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="E48" s="120" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="F48" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="G48" s="120" t="s">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="H48" s="120" t="s">
-        <v>362</v>
+        <v>5</v>
       </c>
       <c r="I48" s="120" t="s">
-        <v>362</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -9725,7 +9728,7 @@
         <v>80</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C49" s="120" t="s">
         <v>53</v>
@@ -9743,10 +9746,10 @@
         <v>148</v>
       </c>
       <c r="H49" s="120" t="s">
-        <v>53</v>
+        <v>361</v>
       </c>
       <c r="I49" s="120" t="s">
-        <v>53</v>
+        <v>361</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -9754,7 +9757,7 @@
         <v>80</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C50" s="120" t="s">
         <v>53</v>
@@ -9783,55 +9786,85 @@
         <v>80</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C51" s="120" t="s">
+        <v>53</v>
+      </c>
+      <c r="D51" s="120" t="s">
+        <v>53</v>
+      </c>
+      <c r="E51" s="120" t="s">
+        <v>54</v>
+      </c>
+      <c r="F51" s="120" t="s">
+        <v>53</v>
+      </c>
+      <c r="G51" s="120" t="s">
+        <v>148</v>
+      </c>
+      <c r="H51" s="120" t="s">
+        <v>53</v>
+      </c>
+      <c r="I51" s="120" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C51" s="120" t="s">
-        <v>53</v>
-      </c>
-      <c r="D51" s="120" t="s">
-        <v>5</v>
-      </c>
-      <c r="E51" s="120" t="s">
-        <v>5</v>
-      </c>
-      <c r="F51" s="120" t="s">
-        <v>5</v>
-      </c>
-      <c r="G51" s="120" t="s">
-        <v>5</v>
-      </c>
-      <c r="H51" s="120" t="s">
-        <v>5</v>
-      </c>
-      <c r="I51" s="120" t="s">
+      <c r="C52" s="120" t="s">
+        <v>53</v>
+      </c>
+      <c r="D52" s="120" t="s">
+        <v>5</v>
+      </c>
+      <c r="E52" s="120" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" s="120" t="s">
+        <v>5</v>
+      </c>
+      <c r="G52" s="120" t="s">
+        <v>5</v>
+      </c>
+      <c r="H52" s="120" t="s">
+        <v>5</v>
+      </c>
+      <c r="I52" s="120" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:I51">
-    <cfRule type="beginsWith" dxfId="15" priority="1" operator="beginsWith" text="Complete">
+  <conditionalFormatting sqref="C2:I52">
+    <cfRule type="beginsWith" dxfId="4" priority="1" operator="beginsWith" text="Complete">
       <formula>LEFT(C2,LEN("Complete"))="Complete"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="Planned">
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Planned">
       <formula>NOT(ISERROR(SEARCH("Planned",C2)))</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="13" priority="3" operator="beginsWith" text="Incomplete">
+    <cfRule type="beginsWith" dxfId="2" priority="3" operator="beginsWith" text="Incomplete">
       <formula>LEFT(C2,LEN("Incomplete"))="Incomplete"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="4" operator="containsText" text="Not Applicable">
+    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Not Applicable">
       <formula>NOT(ISERROR(SEARCH("Not Applicable",C2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="Unknown">
+    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Unknown">
       <formula>NOT(ISERROR(SEARCH("Unknown",C2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" promptTitle="Status" prompt="Pick a status" sqref="J2:J51" xr:uid="{B1E41767-7E01-442E-BF60-264577710112}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" promptTitle="Status" prompt="Pick a status" sqref="J2:J13" xr:uid="{B1E41767-7E01-442E-BF60-264577710112}">
       <formula1>"Complete,In Process,Incomplete/No,N/A,Unknown"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:I51" xr:uid="{D7574FBE-31C9-4FCB-A6FA-5C20C0DF5F52}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:I52" xr:uid="{D7574FBE-31C9-4FCB-A6FA-5C20C0DF5F52}">
       <formula1>"Complete, In Progress/Planned, Incomplete, Not Applicable, Unknown"</formula1>
     </dataValidation>
+    <dataValidation allowBlank="1" promptTitle="Status" prompt="Pick a status" sqref="J14:J52" xr:uid="{4F558D1C-C94C-4FC1-B0B8-BB9E5F10A142}"/>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/clic_data.xlsx
+++ b/clic_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luxxx371\Box\Requests\Clic\Administration\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1CD1A7-15A0-45F6-B49C-9DC725A211D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061E6B36-B134-4CFD-BAF7-AE28F4AAF8F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Total Studies" sheetId="8" r:id="rId1"/>
@@ -1182,9 +1182,6 @@
     <t>Planned</t>
   </si>
   <si>
-    <t>Soutsh Mexican study</t>
-  </si>
-  <si>
     <t>Juan Carlos Núñez-Enríquez</t>
   </si>
   <si>
@@ -1192,6 +1189,9 @@
   </si>
   <si>
     <t>SMS</t>
+  </si>
+  <si>
+    <t>South Mexican study</t>
   </si>
 </sst>
 </file>
@@ -3540,13 +3540,13 @@
         <v>32</v>
       </c>
       <c r="D31" s="70" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E31" s="19" t="s">
         <v>169</v>
       </c>
       <c r="F31" s="127" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G31" s="74" t="s">
         <v>229</v>
@@ -3555,7 +3555,7 @@
         <v>5</v>
       </c>
       <c r="I31" s="70" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9011,7 +9011,7 @@
         <v>32</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C25" s="120" t="s">
         <v>5</v>

--- a/clic_data.xlsx
+++ b/clic_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luxxx371\Box\Requests\Clic\Administration\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061E6B36-B134-4CFD-BAF7-AE28F4AAF8F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{009989F3-7B71-4F19-9C25-FC4E2856C01D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Total Studies" sheetId="8" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2148" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2138" uniqueCount="375">
   <si>
     <t>Country</t>
   </si>
@@ -1119,12 +1119,6 @@
     <t xml:space="preserve">Aim 3 EPI Data Data Avaliability </t>
   </si>
   <si>
-    <t>Phenotype Data Transfer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA-CO Assignment </t>
-  </si>
-  <si>
     <t>RFMIx</t>
   </si>
   <si>
@@ -1188,10 +1182,13 @@
     <t>2021 to 2023</t>
   </si>
   <si>
-    <t>SMS</t>
-  </si>
-  <si>
     <t>South Mexican study</t>
+  </si>
+  <si>
+    <t>CA-CO Matching</t>
+  </si>
+  <si>
+    <t>Phenotype MetaData Transfer</t>
   </si>
 </sst>
 </file>
@@ -3540,13 +3537,13 @@
         <v>32</v>
       </c>
       <c r="D31" s="70" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E31" s="19" t="s">
         <v>169</v>
       </c>
       <c r="F31" s="127" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G31" s="74" t="s">
         <v>229</v>
@@ -3555,7 +3552,7 @@
         <v>5</v>
       </c>
       <c r="I31" s="70" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4279,7 +4276,7 @@
   <sheetData>
     <row r="1" spans="1:13" s="11" customFormat="1" ht="63" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>0</v>
@@ -4469,28 +4466,28 @@
         <v>100</v>
       </c>
       <c r="E1" s="123" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F1" s="123" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="G1" s="119" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="H1" s="118" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="I1" s="26" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="J1" s="26" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="K1" s="117" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="L1" s="117" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="M1" s="26" t="s">
         <v>341</v>
@@ -4502,19 +4499,19 @@
         <v>342</v>
       </c>
       <c r="P1" s="117" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="Q1" s="117" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="R1" s="117" t="s">
         <v>155</v>
       </c>
       <c r="S1" s="117" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="T1" s="117" t="s">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="U1" s="117" t="s">
         <v>99</v>
@@ -4610,7 +4607,7 @@
         <v>169</v>
       </c>
       <c r="F3" s="101" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G3" s="109" t="s">
         <v>348</v>
@@ -4652,7 +4649,7 @@
         <v>349</v>
       </c>
       <c r="T3" s="107" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="U3" s="107" t="s">
         <v>347</v>
@@ -4664,23 +4661,21 @@
     </row>
     <row r="4" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="109" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="B4" s="110" t="s">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C4" s="109" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="D4" s="101" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="E4" s="101" t="s">
-        <v>169</v>
-      </c>
-      <c r="F4" s="101" t="s">
-        <v>366</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="F4" s="101"/>
       <c r="G4" s="109" t="s">
         <v>348</v>
       </c>
@@ -4709,19 +4704,19 @@
         <v>348</v>
       </c>
       <c r="P4" s="107" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q4" s="107" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="R4" s="107" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="S4" s="107" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="T4" s="107" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="U4" s="107" t="s">
         <v>347</v>
@@ -4733,22 +4728,22 @@
     </row>
     <row r="5" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="109" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B5" s="110" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="C5" s="109" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="D5" s="101" t="s">
-        <v>102</v>
+        <v>17</v>
       </c>
       <c r="E5" s="101" t="s">
         <v>182</v>
       </c>
       <c r="F5" s="101" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G5" s="109" t="s">
         <v>348</v>
@@ -4766,31 +4761,31 @@
         <v>348</v>
       </c>
       <c r="L5" s="107" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M5" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="N5" s="108" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O5" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="P5" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q5" s="107" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="R5" s="107" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="S5" s="107" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="T5" s="107" t="s">
-        <v>371</v>
+        <v>348</v>
       </c>
       <c r="U5" s="107" t="s">
         <v>347</v>
@@ -4798,26 +4793,26 @@
       <c r="V5" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="W5" s="106"/>
+      <c r="W5" s="107"/>
     </row>
     <row r="6" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="109" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B6" s="110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="109" t="s">
-        <v>130</v>
-      </c>
-      <c r="D6" s="101" t="s">
-        <v>17</v>
+        <v>80</v>
+      </c>
+      <c r="C6" s="108" t="s">
+        <v>368</v>
+      </c>
+      <c r="D6" s="124" t="s">
+        <v>367</v>
       </c>
       <c r="E6" s="101" t="s">
         <v>182</v>
       </c>
       <c r="F6" s="101" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G6" s="109" t="s">
         <v>348</v>
@@ -4835,31 +4830,31 @@
         <v>348</v>
       </c>
       <c r="L6" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="M6" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="N6" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="O6" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="P6" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q6" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="R6" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="S6" s="107" t="s">
         <v>349</v>
       </c>
-      <c r="M6" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="N6" s="108" t="s">
-        <v>347</v>
-      </c>
-      <c r="O6" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="P6" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="Q6" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="R6" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="S6" s="107" t="s">
-        <v>347</v>
-      </c>
       <c r="T6" s="107" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="U6" s="107" t="s">
         <v>347</v>
@@ -4867,7 +4862,7 @@
       <c r="V6" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="W6" s="107"/>
+      <c r="W6" s="106"/>
     </row>
     <row r="7" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="109" t="s">
@@ -4883,7 +4878,7 @@
         <v>104</v>
       </c>
       <c r="E7" s="114" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F7" s="114"/>
       <c r="G7" s="113" t="s">
@@ -4934,23 +4929,23 @@
     </row>
     <row r="8" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="109" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B8" s="110" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="C8" s="108" t="s">
-        <v>132</v>
+        <v>368</v>
       </c>
       <c r="D8" s="101" t="s">
-        <v>116</v>
-      </c>
-      <c r="E8" s="124" t="s">
-        <v>235</v>
-      </c>
-      <c r="F8" s="124" t="s">
         <v>366</v>
       </c>
+      <c r="E8" s="101" t="s">
+        <v>182</v>
+      </c>
+      <c r="F8" s="101" t="s">
+        <v>364</v>
+      </c>
       <c r="G8" s="109" t="s">
         <v>348</v>
       </c>
@@ -4976,22 +4971,22 @@
         <v>348</v>
       </c>
       <c r="O8" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="P8" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q8" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="R8" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="S8" s="107" t="s">
         <v>349</v>
       </c>
-      <c r="P8" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="Q8" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="R8" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="S8" s="107" t="s">
-        <v>347</v>
-      </c>
       <c r="T8" s="107" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="U8" s="107" t="s">
         <v>347</v>
@@ -4999,7 +4994,7 @@
       <c r="V8" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="W8" s="107"/>
+      <c r="W8" s="106"/>
     </row>
     <row r="9" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="109" t="s">
@@ -5012,30 +5007,30 @@
         <v>132</v>
       </c>
       <c r="D9" s="101" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E9" s="124" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F9" s="124" t="s">
-        <v>366</v>
-      </c>
-      <c r="G9" s="115" t="s">
+        <v>364</v>
+      </c>
+      <c r="G9" s="109" t="s">
         <v>348</v>
       </c>
       <c r="H9" s="109" t="s">
         <v>348</v>
       </c>
-      <c r="I9" s="109" t="s">
+      <c r="I9" s="107" t="s">
         <v>348</v>
       </c>
       <c r="J9" s="109" t="s">
         <v>348</v>
       </c>
-      <c r="K9" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="L9" s="109" t="s">
+      <c r="K9" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="L9" s="107" t="s">
         <v>348</v>
       </c>
       <c r="M9" s="107" t="s">
@@ -5044,13 +5039,13 @@
       <c r="N9" s="108" t="s">
         <v>348</v>
       </c>
-      <c r="O9" s="109" t="s">
+      <c r="O9" s="107" t="s">
         <v>349</v>
       </c>
       <c r="P9" s="107" t="s">
         <v>347</v>
       </c>
-      <c r="Q9" s="109" t="s">
+      <c r="Q9" s="107" t="s">
         <v>348</v>
       </c>
       <c r="R9" s="107" t="s">
@@ -5072,141 +5067,141 @@
     </row>
     <row r="10" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="109" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B10" s="110" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="109" t="s">
-        <v>133</v>
+        <v>21</v>
+      </c>
+      <c r="C10" s="108" t="s">
+        <v>132</v>
       </c>
       <c r="D10" s="101" t="s">
-        <v>118</v>
-      </c>
-      <c r="E10" s="101" t="s">
-        <v>182</v>
-      </c>
-      <c r="F10" s="101" t="s">
-        <v>366</v>
+        <v>117</v>
+      </c>
+      <c r="E10" s="124" t="s">
+        <v>238</v>
+      </c>
+      <c r="F10" s="124" t="s">
+        <v>364</v>
       </c>
       <c r="G10" s="115" t="s">
         <v>348</v>
       </c>
-      <c r="H10" s="113" t="s">
-        <v>348</v>
-      </c>
-      <c r="I10" s="111" t="s">
-        <v>348</v>
-      </c>
-      <c r="J10" s="113" t="s">
-        <v>348</v>
-      </c>
-      <c r="K10" s="111" t="s">
-        <v>348</v>
-      </c>
-      <c r="L10" s="111" t="s">
-        <v>348</v>
-      </c>
-      <c r="M10" s="111" t="s">
-        <v>348</v>
-      </c>
-      <c r="N10" s="112" t="s">
-        <v>348</v>
-      </c>
-      <c r="O10" s="111" t="s">
-        <v>348</v>
-      </c>
-      <c r="P10" s="111" t="s">
-        <v>347</v>
-      </c>
-      <c r="Q10" s="111" t="s">
-        <v>348</v>
-      </c>
-      <c r="R10" s="111" t="s">
-        <v>347</v>
-      </c>
-      <c r="S10" s="111" t="s">
-        <v>347</v>
-      </c>
-      <c r="T10" s="111" t="s">
-        <v>371</v>
-      </c>
-      <c r="U10" s="111" t="s">
+      <c r="H10" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="I10" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="J10" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="K10" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="L10" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="M10" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="N10" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="O10" s="109" t="s">
+        <v>349</v>
+      </c>
+      <c r="P10" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q10" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="R10" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="S10" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="T10" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="U10" s="107" t="s">
         <v>347</v>
       </c>
       <c r="V10" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="W10" s="106"/>
+      <c r="W10" s="107"/>
     </row>
     <row r="11" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="109" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B11" s="110" t="s">
-        <v>137</v>
+        <v>31</v>
       </c>
       <c r="C11" s="109" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D11" s="101" t="s">
-        <v>346</v>
+        <v>118</v>
       </c>
       <c r="E11" s="101" t="s">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="F11" s="101" t="s">
-        <v>366</v>
-      </c>
-      <c r="G11" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="H11" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="I11" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="J11" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="K11" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="L11" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="M11" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="N11" s="108" t="s">
-        <v>347</v>
-      </c>
-      <c r="O11" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="P11" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="Q11" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="R11" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="S11" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="T11" s="107" t="s">
-        <v>371</v>
-      </c>
-      <c r="U11" s="107" t="s">
+        <v>364</v>
+      </c>
+      <c r="G11" s="115" t="s">
+        <v>348</v>
+      </c>
+      <c r="H11" s="113" t="s">
+        <v>348</v>
+      </c>
+      <c r="I11" s="111" t="s">
+        <v>348</v>
+      </c>
+      <c r="J11" s="113" t="s">
+        <v>348</v>
+      </c>
+      <c r="K11" s="111" t="s">
+        <v>348</v>
+      </c>
+      <c r="L11" s="111" t="s">
+        <v>348</v>
+      </c>
+      <c r="M11" s="111" t="s">
+        <v>348</v>
+      </c>
+      <c r="N11" s="112" t="s">
+        <v>348</v>
+      </c>
+      <c r="O11" s="111" t="s">
+        <v>348</v>
+      </c>
+      <c r="P11" s="111" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q11" s="111" t="s">
+        <v>348</v>
+      </c>
+      <c r="R11" s="111" t="s">
+        <v>347</v>
+      </c>
+      <c r="S11" s="111" t="s">
+        <v>347</v>
+      </c>
+      <c r="T11" s="111" t="s">
+        <v>369</v>
+      </c>
+      <c r="U11" s="111" t="s">
         <v>347</v>
       </c>
       <c r="V11" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="W11" s="107"/>
+      <c r="W11" s="106"/>
     </row>
     <row r="12" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="109" t="s">
@@ -5215,17 +5210,17 @@
       <c r="B12" s="110" t="s">
         <v>80</v>
       </c>
-      <c r="C12" s="108" t="s">
-        <v>370</v>
-      </c>
-      <c r="D12" s="124" t="s">
-        <v>369</v>
+      <c r="C12" s="109" t="s">
+        <v>125</v>
+      </c>
+      <c r="D12" s="101" t="s">
+        <v>107</v>
       </c>
       <c r="E12" s="101" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="F12" s="101" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G12" s="109" t="s">
         <v>348</v>
@@ -5236,7 +5231,7 @@
       <c r="I12" s="107" t="s">
         <v>348</v>
       </c>
-      <c r="J12" s="109" t="s">
+      <c r="J12" s="116" t="s">
         <v>348</v>
       </c>
       <c r="K12" s="107" t="s">
@@ -5267,7 +5262,7 @@
         <v>349</v>
       </c>
       <c r="T12" s="107" t="s">
-        <v>371</v>
+        <v>348</v>
       </c>
       <c r="U12" s="107" t="s">
         <v>347</v>
@@ -5284,17 +5279,17 @@
       <c r="B13" s="110" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="108" t="s">
-        <v>370</v>
+      <c r="C13" s="109" t="s">
+        <v>125</v>
       </c>
       <c r="D13" s="101" t="s">
-        <v>368</v>
+        <v>28</v>
       </c>
       <c r="E13" s="101" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="F13" s="101" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G13" s="109" t="s">
         <v>348</v>
@@ -5336,7 +5331,7 @@
         <v>349</v>
       </c>
       <c r="T13" s="107" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="U13" s="107" t="s">
         <v>347</v>
@@ -5543,16 +5538,16 @@
         <v>80</v>
       </c>
       <c r="C17" s="109" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D17" s="101" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E17" s="101" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="F17" s="101" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G17" s="109" t="s">
         <v>348</v>
@@ -5563,7 +5558,7 @@
       <c r="I17" s="107" t="s">
         <v>348</v>
       </c>
-      <c r="J17" s="116" t="s">
+      <c r="J17" s="109" t="s">
         <v>348</v>
       </c>
       <c r="K17" s="107" t="s">
@@ -5661,7 +5656,7 @@
         <v>347</v>
       </c>
       <c r="T18" s="107" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="U18" s="107" t="s">
         <v>347</v>
@@ -5679,16 +5674,16 @@
         <v>80</v>
       </c>
       <c r="C19" s="109" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D19" s="101" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="E19" s="101" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="F19" s="101" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G19" s="109" t="s">
         <v>348</v>
@@ -5730,7 +5725,7 @@
         <v>349</v>
       </c>
       <c r="T19" s="107" t="s">
-        <v>371</v>
+        <v>348</v>
       </c>
       <c r="U19" s="107" t="s">
         <v>347</v>
@@ -5860,7 +5855,7 @@
         <v>347</v>
       </c>
       <c r="T21" s="107" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="U21" s="107" t="s">
         <v>347</v>
@@ -5881,13 +5876,13 @@
         <v>126</v>
       </c>
       <c r="D22" s="101" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E22" s="101" t="s">
         <v>182</v>
       </c>
       <c r="F22" s="101" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G22" s="109" t="s">
         <v>348</v>
@@ -5944,88 +5939,86 @@
         <v>129</v>
       </c>
       <c r="B23" s="110" t="s">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="C23" s="109" t="s">
-        <v>126</v>
-      </c>
-      <c r="D23" s="101" t="s">
-        <v>110</v>
-      </c>
-      <c r="E23" s="101" t="s">
+        <v>127</v>
+      </c>
+      <c r="D23" s="114" t="s">
+        <v>114</v>
+      </c>
+      <c r="E23" s="114" t="s">
         <v>182</v>
       </c>
-      <c r="F23" s="101" t="s">
-        <v>366</v>
-      </c>
-      <c r="G23" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="H23" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="I23" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="J23" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="K23" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="L23" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="M23" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="N23" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="O23" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="P23" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="Q23" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="R23" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="S23" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="T23" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="U23" s="107" t="s">
+      <c r="F23" s="114" t="s">
+        <v>364</v>
+      </c>
+      <c r="G23" s="113" t="s">
+        <v>348</v>
+      </c>
+      <c r="H23" s="113" t="s">
+        <v>348</v>
+      </c>
+      <c r="I23" s="111"/>
+      <c r="J23" s="113"/>
+      <c r="K23" s="113" t="s">
+        <v>348</v>
+      </c>
+      <c r="L23" s="113" t="s">
+        <v>348</v>
+      </c>
+      <c r="M23" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="N23" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="O23" s="113" t="s">
+        <v>348</v>
+      </c>
+      <c r="P23" s="113" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q23" s="113" t="s">
+        <v>348</v>
+      </c>
+      <c r="R23" s="113" t="s">
+        <v>348</v>
+      </c>
+      <c r="S23" s="113" t="s">
+        <v>347</v>
+      </c>
+      <c r="T23" s="113" t="s">
+        <v>347</v>
+      </c>
+      <c r="U23" s="113" t="s">
         <v>347</v>
       </c>
       <c r="V23" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="W23" s="106"/>
+      <c r="W23" s="106" t="s">
+        <v>345</v>
+      </c>
     </row>
     <row r="24" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="109" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B24" s="110" t="s">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C24" s="109" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="D24" s="101" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E24" s="101" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="F24" s="101" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G24" s="109" t="s">
         <v>348</v>
@@ -6055,16 +6048,16 @@
         <v>348</v>
       </c>
       <c r="P24" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q24" s="107" t="s">
         <v>348</v>
       </c>
       <c r="R24" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="S24" s="107" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="T24" s="107" t="s">
         <v>348</v>
@@ -6091,7 +6084,7 @@
         <v>111</v>
       </c>
       <c r="E25" s="114" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F25" s="114"/>
       <c r="G25" s="113" t="s">
@@ -6145,92 +6138,94 @@
         <v>129</v>
       </c>
       <c r="B26" s="110" t="s">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="C26" s="109" t="s">
-        <v>127</v>
-      </c>
-      <c r="D26" s="114" t="s">
-        <v>114</v>
-      </c>
-      <c r="E26" s="114" t="s">
+        <v>129</v>
+      </c>
+      <c r="D26" s="101" t="s">
+        <v>115</v>
+      </c>
+      <c r="E26" s="101" t="s">
         <v>182</v>
       </c>
-      <c r="F26" s="114" t="s">
-        <v>366</v>
-      </c>
-      <c r="G26" s="113" t="s">
-        <v>348</v>
-      </c>
-      <c r="H26" s="113" t="s">
-        <v>348</v>
-      </c>
-      <c r="I26" s="111"/>
-      <c r="J26" s="113"/>
-      <c r="K26" s="113" t="s">
-        <v>348</v>
-      </c>
-      <c r="L26" s="113" t="s">
-        <v>348</v>
-      </c>
-      <c r="M26" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="N26" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="O26" s="113" t="s">
-        <v>348</v>
-      </c>
-      <c r="P26" s="113" t="s">
-        <v>348</v>
-      </c>
-      <c r="Q26" s="113" t="s">
-        <v>348</v>
-      </c>
-      <c r="R26" s="113" t="s">
-        <v>348</v>
-      </c>
-      <c r="S26" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="T26" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="U26" s="113" t="s">
-        <v>5</v>
+      <c r="F26" s="101" t="s">
+        <v>364</v>
+      </c>
+      <c r="G26" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="H26" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="I26" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="J26" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="K26" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="L26" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="M26" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="N26" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="O26" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="P26" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q26" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="R26" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="S26" s="107" t="s">
+        <v>349</v>
+      </c>
+      <c r="T26" s="107" t="s">
+        <v>369</v>
+      </c>
+      <c r="U26" s="107" t="s">
+        <v>347</v>
       </c>
       <c r="V26" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="W26" s="106" t="s">
-        <v>345</v>
-      </c>
+      <c r="W26" s="107"/>
     </row>
     <row r="27" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="109" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B27" s="110" t="s">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="C27" s="109" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D27" s="101" t="s">
-        <v>115</v>
+        <v>346</v>
       </c>
       <c r="E27" s="101" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="F27" s="101" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G27" s="109" t="s">
         <v>348</v>
       </c>
       <c r="H27" s="109" t="s">
-        <v>348</v>
+        <v>148</v>
       </c>
       <c r="I27" s="107" t="s">
         <v>348</v>
@@ -6239,34 +6234,34 @@
         <v>348</v>
       </c>
       <c r="K27" s="107" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L27" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="M27" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="N27" s="108" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O27" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="P27" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q27" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="R27" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="S27" s="107" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="T27" s="107" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="U27" s="107" t="s">
         <v>347</v>
@@ -8272,7 +8267,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -8370,7 +8365,7 @@
         <v>53</v>
       </c>
       <c r="I3" s="120" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J3" s="4"/>
     </row>
@@ -8460,7 +8455,7 @@
         <v>53</v>
       </c>
       <c r="I6" s="120" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J6" s="4"/>
     </row>
@@ -8481,7 +8476,7 @@
         <v>53</v>
       </c>
       <c r="F7" s="120" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G7" s="120" t="s">
         <v>148</v>
@@ -8520,7 +8515,7 @@
         <v>53</v>
       </c>
       <c r="I8" s="120" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J8" s="4"/>
     </row>
@@ -8580,7 +8575,7 @@
         <v>53</v>
       </c>
       <c r="I10" s="120" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J10" s="4"/>
     </row>
@@ -8610,7 +8605,7 @@
         <v>53</v>
       </c>
       <c r="I11" s="120" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J11" s="4"/>
     </row>
@@ -8625,13 +8620,13 @@
         <v>53</v>
       </c>
       <c r="D12" s="120" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E12" s="120" t="s">
         <v>54</v>
       </c>
       <c r="F12" s="120" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G12" s="120" t="s">
         <v>148</v>
@@ -8640,7 +8635,7 @@
         <v>53</v>
       </c>
       <c r="I12" s="120" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J12" s="4"/>
     </row>
@@ -8661,16 +8656,16 @@
         <v>54</v>
       </c>
       <c r="F13" s="120" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G13" s="120" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="H13" s="120" t="s">
         <v>53</v>
       </c>
       <c r="I13" s="120" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -8722,7 +8717,7 @@
         <v>54</v>
       </c>
       <c r="F15" s="120" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G15" s="120" t="s">
         <v>148</v>
@@ -8731,7 +8726,7 @@
         <v>53</v>
       </c>
       <c r="I15" s="120" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>20</v>
@@ -8883,7 +8878,7 @@
         <v>53</v>
       </c>
       <c r="I20" s="120" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J20" s="4"/>
     </row>
@@ -9008,71 +9003,74 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>374</v>
+        <v>35</v>
       </c>
       <c r="C25" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D25" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="E25" s="120" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="F25" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="G25" s="120" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="H25" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="I25" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C26" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="D26" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="E26" s="120" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="F26" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="G26" s="120" t="s">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="H26" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="I26" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C27" s="120" t="s">
         <v>5</v>
@@ -9094,188 +9092,186 @@
       </c>
       <c r="I27" s="120" t="s">
         <v>5</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C28" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D28" s="120" t="s">
-        <v>5</v>
+        <v>359</v>
       </c>
       <c r="E28" s="120" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="F28" s="120" t="s">
-        <v>5</v>
+        <v>359</v>
       </c>
       <c r="G28" s="120" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="H28" s="120" t="s">
-        <v>5</v>
+        <v>359</v>
       </c>
       <c r="I28" s="120" t="s">
-        <v>5</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="J28" s="4"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C29" s="120" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D29" s="120" t="s">
-        <v>361</v>
+        <v>148</v>
       </c>
       <c r="E29" s="120" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="F29" s="120" t="s">
-        <v>361</v>
+        <v>148</v>
       </c>
       <c r="G29" s="120" t="s">
         <v>148</v>
       </c>
       <c r="H29" s="120" t="s">
-        <v>361</v>
+        <v>148</v>
       </c>
       <c r="I29" s="120" t="s">
-        <v>361</v>
-      </c>
-      <c r="J29" s="4"/>
+        <v>148</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" s="120" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="D30" s="120" t="s">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="E30" s="120" t="s">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="F30" s="120" t="s">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="G30" s="120" t="s">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="H30" s="120" t="s">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="I30" s="120" t="s">
-        <v>148</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="J30" s="4"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>137</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="C31" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D31" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="E31" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="F31" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="G31" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="H31" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="I31" s="120" t="s">
-        <v>5</v>
-      </c>
-      <c r="J31" s="4"/>
+        <v>53</v>
+      </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>137</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C32" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="D32" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="E32" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="F32" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="G32" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="H32" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="I32" s="120" t="s">
-        <v>53</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="J32" s="4"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="C33" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D33" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="E33" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="F33" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="G33" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="H33" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="I33" s="120" t="s">
-        <v>5</v>
+        <v>359</v>
       </c>
       <c r="J33" s="4"/>
     </row>
@@ -9284,90 +9280,90 @@
         <v>80</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="C34" s="120" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D34" s="120" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="E34" s="120" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="F34" s="120" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="G34" s="120" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H34" s="120" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="I34" s="120" t="s">
-        <v>361</v>
-      </c>
-      <c r="J34" s="4"/>
+        <v>148</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>80</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C35" s="120" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="D35" s="120" t="s">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="E35" s="120" t="s">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="F35" s="120" t="s">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="G35" s="120" t="s">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="H35" s="120" t="s">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="I35" s="120" t="s">
-        <v>148</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="J35" s="4"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>80</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C36" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D36" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="E36" s="120" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="F36" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="G36" s="120" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="H36" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="I36" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="J36" s="4"/>
     </row>
@@ -9376,7 +9372,7 @@
         <v>80</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C37" s="120" t="s">
         <v>53</v>
@@ -9406,7 +9402,7 @@
         <v>80</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C38" s="120" t="s">
         <v>53</v>
@@ -9436,7 +9432,7 @@
         <v>80</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C39" s="120" t="s">
         <v>53</v>
@@ -9466,7 +9462,7 @@
         <v>80</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C40" s="120" t="s">
         <v>53</v>
@@ -9489,14 +9485,13 @@
       <c r="I40" s="120" t="s">
         <v>53</v>
       </c>
-      <c r="J40" s="4"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>80</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C41" s="120" t="s">
         <v>53</v>
@@ -9525,28 +9520,28 @@
         <v>80</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C42" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="D42" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="E42" s="120" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="F42" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="G42" s="120" t="s">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="H42" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="I42" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -9554,28 +9549,28 @@
         <v>80</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C43" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D43" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="E43" s="120" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="F43" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="G43" s="120" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="H43" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="I43" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -9583,7 +9578,7 @@
         <v>80</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C44" s="120" t="s">
         <v>53</v>
@@ -9612,28 +9607,28 @@
         <v>80</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="C45" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="D45" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="E45" s="120" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="F45" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="G45" s="120" t="s">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="H45" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="I45" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -9641,28 +9636,28 @@
         <v>80</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="C46" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D46" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="E46" s="120" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="F46" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="G46" s="120" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="H46" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="I46" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -9670,28 +9665,28 @@
         <v>80</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C47" s="120" t="s">
         <v>53</v>
       </c>
       <c r="D47" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="E47" s="120" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="F47" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="G47" s="120" t="s">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="H47" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="I47" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -9699,28 +9694,28 @@
         <v>80</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C48" s="120" t="s">
         <v>53</v>
       </c>
       <c r="D48" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="E48" s="120" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="F48" s="120" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="G48" s="120" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="H48" s="120" t="s">
-        <v>5</v>
+        <v>359</v>
       </c>
       <c r="I48" s="120" t="s">
-        <v>5</v>
+        <v>359</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -9728,7 +9723,7 @@
         <v>80</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C49" s="120" t="s">
         <v>53</v>
@@ -9746,10 +9741,10 @@
         <v>148</v>
       </c>
       <c r="H49" s="120" t="s">
-        <v>361</v>
+        <v>53</v>
       </c>
       <c r="I49" s="120" t="s">
-        <v>361</v>
+        <v>53</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -9757,7 +9752,7 @@
         <v>80</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C50" s="120" t="s">
         <v>53</v>
@@ -9786,61 +9781,32 @@
         <v>80</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C51" s="120" t="s">
         <v>53</v>
       </c>
       <c r="D51" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="E51" s="120" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="F51" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="G51" s="120" t="s">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="H51" s="120" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="I51" s="120" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C52" s="120" t="s">
-        <v>53</v>
-      </c>
-      <c r="D52" s="120" t="s">
-        <v>5</v>
-      </c>
-      <c r="E52" s="120" t="s">
-        <v>5</v>
-      </c>
-      <c r="F52" s="120" t="s">
-        <v>5</v>
-      </c>
-      <c r="G52" s="120" t="s">
-        <v>5</v>
-      </c>
-      <c r="H52" s="120" t="s">
-        <v>5</v>
-      </c>
-      <c r="I52" s="120" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:I52">
+  <conditionalFormatting sqref="C2:I51">
     <cfRule type="beginsWith" dxfId="4" priority="1" operator="beginsWith" text="Complete">
       <formula>LEFT(C2,LEN("Complete"))="Complete"</formula>
     </cfRule>
@@ -9861,10 +9827,10 @@
     <dataValidation type="list" allowBlank="1" promptTitle="Status" prompt="Pick a status" sqref="J2:J13" xr:uid="{B1E41767-7E01-442E-BF60-264577710112}">
       <formula1>"Complete,In Process,Incomplete/No,N/A,Unknown"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:I52" xr:uid="{D7574FBE-31C9-4FCB-A6FA-5C20C0DF5F52}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:I51" xr:uid="{D7574FBE-31C9-4FCB-A6FA-5C20C0DF5F52}">
       <formula1>"Complete, In Progress/Planned, Incomplete, Not Applicable, Unknown"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" promptTitle="Status" prompt="Pick a status" sqref="J14:J52" xr:uid="{4F558D1C-C94C-4FC1-B0B8-BB9E5F10A142}"/>
+    <dataValidation allowBlank="1" promptTitle="Status" prompt="Pick a status" sqref="J14:J51" xr:uid="{4F558D1C-C94C-4FC1-B0B8-BB9E5F10A142}"/>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/clic_data.xlsx
+++ b/clic_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luxxx371\Box\Requests\Clic\Administration\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{009989F3-7B71-4F19-9C25-FC4E2856C01D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDEB4527-E162-494F-93AE-23F75316D6A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Total Studies" sheetId="8" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="IARC DCC Transfer" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Genomic Pipeline'!$A$1:$W$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Genomic Pipeline'!$A$1:$X$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Phenotype Data'!$A$1:$L$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Total Studies'!$A$1:$I$55</definedName>
   </definedNames>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2138" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="376">
   <si>
     <t>Country</t>
   </si>
@@ -1189,6 +1189,9 @@
   </si>
   <si>
     <t>Phenotype MetaData Transfer</t>
+  </si>
+  <si>
+    <t>Proposed Cases</t>
   </si>
 </sst>
 </file>
@@ -1331,7 +1334,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1418,6 +1421,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1805,7 +1820,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2182,6 +2197,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4430,7 +4451,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED25CF60-E519-46A5-8820-1361CFDEEEDA}">
-  <dimension ref="A1:W27"/>
+  <dimension ref="A1:X27"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.7109375" style="102" customWidth="1"/>
@@ -4438,21 +4459,21 @@
     <col min="3" max="3" width="46.140625" style="102" customWidth="1"/>
     <col min="4" max="4" width="26" style="103" customWidth="1"/>
     <col min="5" max="5" width="34.5703125" style="103" customWidth="1"/>
-    <col min="6" max="6" width="19.5703125" style="103" customWidth="1"/>
-    <col min="7" max="7" width="26" style="103" customWidth="1"/>
-    <col min="8" max="8" width="27.42578125" style="103" customWidth="1"/>
-    <col min="9" max="10" width="22.5703125" style="103" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="16.5703125" style="103" customWidth="1"/>
-    <col min="12" max="12" width="15" style="103" customWidth="1"/>
-    <col min="13" max="14" width="13.140625" style="103" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="15" style="103" customWidth="1"/>
-    <col min="16" max="16" width="19.140625" style="103" customWidth="1"/>
-    <col min="17" max="22" width="15" style="103" customWidth="1"/>
-    <col min="23" max="23" width="16" style="102" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="102"/>
+    <col min="6" max="7" width="19.5703125" style="103" customWidth="1"/>
+    <col min="8" max="8" width="26" style="103" customWidth="1"/>
+    <col min="9" max="9" width="27.42578125" style="103" customWidth="1"/>
+    <col min="10" max="11" width="22.5703125" style="103" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5703125" style="103" customWidth="1"/>
+    <col min="13" max="13" width="15" style="103" customWidth="1"/>
+    <col min="14" max="15" width="13.140625" style="103" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="15" style="103" customWidth="1"/>
+    <col min="17" max="17" width="19.140625" style="103" customWidth="1"/>
+    <col min="18" max="23" width="15" style="103" customWidth="1"/>
+    <col min="24" max="24" width="16" style="102" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="102"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="103" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="103" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
         <v>135</v>
       </c>
@@ -4471,59 +4492,62 @@
       <c r="F1" s="123" t="s">
         <v>365</v>
       </c>
-      <c r="G1" s="119" t="s">
+      <c r="G1" s="123" t="s">
+        <v>375</v>
+      </c>
+      <c r="H1" s="119" t="s">
         <v>358</v>
       </c>
-      <c r="H1" s="118" t="s">
+      <c r="I1" s="118" t="s">
         <v>357</v>
       </c>
-      <c r="I1" s="26" t="s">
+      <c r="J1" s="26" t="s">
         <v>356</v>
       </c>
-      <c r="J1" s="26" t="s">
+      <c r="K1" s="26" t="s">
         <v>355</v>
       </c>
-      <c r="K1" s="117" t="s">
+      <c r="L1" s="117" t="s">
         <v>354</v>
       </c>
-      <c r="L1" s="117" t="s">
+      <c r="M1" s="117" t="s">
         <v>353</v>
       </c>
-      <c r="M1" s="26" t="s">
+      <c r="N1" s="26" t="s">
         <v>341</v>
       </c>
-      <c r="N1" s="26" t="s">
+      <c r="O1" s="26" t="s">
         <v>151</v>
       </c>
-      <c r="O1" s="117" t="s">
+      <c r="P1" s="117" t="s">
         <v>342</v>
       </c>
-      <c r="P1" s="117" t="s">
+      <c r="Q1" s="117" t="s">
         <v>352</v>
       </c>
-      <c r="Q1" s="117" t="s">
+      <c r="R1" s="117" t="s">
         <v>351</v>
       </c>
-      <c r="R1" s="117" t="s">
+      <c r="S1" s="117" t="s">
         <v>155</v>
       </c>
-      <c r="S1" s="117" t="s">
+      <c r="T1" s="117" t="s">
         <v>373</v>
       </c>
-      <c r="T1" s="117" t="s">
+      <c r="U1" s="117" t="s">
         <v>374</v>
       </c>
-      <c r="U1" s="117" t="s">
+      <c r="V1" s="117" t="s">
         <v>99</v>
       </c>
-      <c r="V1" s="117" t="s">
+      <c r="W1" s="117" t="s">
         <v>350</v>
       </c>
-      <c r="W1" s="26" t="s">
+      <c r="X1" s="26" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="109" t="s">
         <v>129</v>
       </c>
@@ -4534,83 +4558,88 @@
         <v>122</v>
       </c>
       <c r="D2" s="101" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E2" s="101" t="s">
-        <v>196</v>
-      </c>
-      <c r="F2" s="101"/>
-      <c r="G2" s="109" t="s">
-        <v>348</v>
+        <v>169</v>
+      </c>
+      <c r="F2" s="101" t="s">
+        <v>364</v>
+      </c>
+      <c r="G2" s="129">
+        <v>1692</v>
       </c>
       <c r="H2" s="109" t="s">
         <v>348</v>
       </c>
-      <c r="I2" s="107" t="s">
+      <c r="I2" s="109" t="s">
         <v>348</v>
       </c>
       <c r="J2" s="109" t="s">
         <v>348</v>
       </c>
-      <c r="K2" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="L2" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="M2" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="N2" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="O2" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="P2" s="107" t="s">
-        <v>347</v>
+      <c r="K2" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="L2" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="M2" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="N2" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="O2" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="P2" s="109" t="s">
+        <v>348</v>
       </c>
       <c r="Q2" s="107" t="s">
         <v>348</v>
       </c>
-      <c r="R2" s="107" t="s">
-        <v>347</v>
+      <c r="R2" s="109" t="s">
+        <v>348</v>
       </c>
       <c r="S2" s="107" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="T2" s="107" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="U2" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="V2" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="W2" s="106"/>
-    </row>
-    <row r="3" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+      <c r="V2" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="W2" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="X2" s="106"/>
+    </row>
+    <row r="3" spans="1:24" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="109" t="s">
         <v>129</v>
       </c>
       <c r="B3" s="110" t="s">
         <v>80</v>
       </c>
-      <c r="C3" s="109" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="101" t="s">
-        <v>101</v>
+      <c r="C3" s="108" t="s">
+        <v>368</v>
+      </c>
+      <c r="D3" s="124" t="s">
+        <v>367</v>
       </c>
       <c r="E3" s="101" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="F3" s="101" t="s">
         <v>364</v>
       </c>
-      <c r="G3" s="109" t="s">
-        <v>348</v>
+      <c r="G3" s="101">
+        <v>3834</v>
       </c>
       <c r="H3" s="109" t="s">
         <v>348</v>
@@ -4618,48 +4647,51 @@
       <c r="I3" s="109" t="s">
         <v>348</v>
       </c>
-      <c r="J3" s="109" t="s">
+      <c r="J3" s="107" t="s">
         <v>348</v>
       </c>
       <c r="K3" s="109" t="s">
         <v>348</v>
       </c>
-      <c r="L3" s="109" t="s">
+      <c r="L3" s="107" t="s">
         <v>348</v>
       </c>
       <c r="M3" s="107" t="s">
         <v>348</v>
       </c>
-      <c r="N3" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="O3" s="109" t="s">
+      <c r="N3" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="O3" s="108" t="s">
         <v>348</v>
       </c>
       <c r="P3" s="107" t="s">
         <v>348</v>
       </c>
-      <c r="Q3" s="109" t="s">
+      <c r="Q3" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="R3" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="S3" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="T3" s="107" t="s">
         <v>349</v>
       </c>
-      <c r="R3" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="S3" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="T3" s="107" t="s">
+      <c r="U3" s="107" t="s">
         <v>369</v>
       </c>
-      <c r="U3" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="V3" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="W3" s="106"/>
-    </row>
-    <row r="4" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V3" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="W3" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="X3" s="106"/>
+    </row>
+    <row r="4" spans="1:24" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="109" t="s">
         <v>129</v>
       </c>
@@ -4667,28 +4699,30 @@
         <v>80</v>
       </c>
       <c r="C4" s="109" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D4" s="101" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E4" s="101" t="s">
-        <v>314</v>
-      </c>
-      <c r="F4" s="101"/>
-      <c r="G4" s="109" t="s">
-        <v>348</v>
+        <v>169</v>
+      </c>
+      <c r="F4" s="101" t="s">
+        <v>364</v>
+      </c>
+      <c r="G4" s="101">
+        <v>1125</v>
       </c>
       <c r="H4" s="109" t="s">
         <v>348</v>
       </c>
-      <c r="I4" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="J4" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="K4" s="107" t="s">
+      <c r="I4" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="J4" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="K4" s="116" t="s">
         <v>348</v>
       </c>
       <c r="L4" s="107" t="s">
@@ -4697,116 +4731,122 @@
       <c r="M4" s="107" t="s">
         <v>348</v>
       </c>
-      <c r="N4" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="O4" s="107" t="s">
+      <c r="N4" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="O4" s="108" t="s">
         <v>348</v>
       </c>
       <c r="P4" s="107" t="s">
         <v>348</v>
       </c>
       <c r="Q4" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="R4" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="S4" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="T4" s="107" t="s">
         <v>349</v>
       </c>
-      <c r="R4" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="S4" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="T4" s="107" t="s">
-        <v>369</v>
-      </c>
       <c r="U4" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="V4" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="W4" s="106"/>
-    </row>
-    <row r="5" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>348</v>
+      </c>
+      <c r="V4" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="W4" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="X4" s="106"/>
+    </row>
+    <row r="5" spans="1:24" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="109" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B5" s="110" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="C5" s="109" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D5" s="101" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E5" s="101" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="F5" s="101" t="s">
         <v>364</v>
       </c>
-      <c r="G5" s="109" t="s">
-        <v>348</v>
+      <c r="G5" s="101">
+        <v>45</v>
       </c>
       <c r="H5" s="109" t="s">
         <v>348</v>
       </c>
-      <c r="I5" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="J5" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="K5" s="107" t="s">
+      <c r="I5" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="J5" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="K5" s="109" t="s">
         <v>348</v>
       </c>
       <c r="L5" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="M5" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="N5" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="O5" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="P5" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q5" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="R5" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="S5" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="T5" s="107" t="s">
         <v>349</v>
       </c>
-      <c r="M5" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="N5" s="108" t="s">
-        <v>347</v>
-      </c>
-      <c r="O5" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="P5" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="Q5" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="R5" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="S5" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="T5" s="107" t="s">
-        <v>348</v>
-      </c>
       <c r="U5" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="V5" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="W5" s="107"/>
-    </row>
-    <row r="6" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+      <c r="V5" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="W5" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="X5" s="106"/>
+    </row>
+    <row r="6" spans="1:24" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="109" t="s">
         <v>129</v>
       </c>
       <c r="B6" s="110" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="108" t="s">
-        <v>368</v>
-      </c>
-      <c r="D6" s="124" t="s">
-        <v>367</v>
+      <c r="C6" s="109" t="s">
+        <v>126</v>
+      </c>
+      <c r="D6" s="101" t="s">
+        <v>109</v>
       </c>
       <c r="E6" s="101" t="s">
         <v>182</v>
@@ -4814,19 +4854,19 @@
       <c r="F6" s="101" t="s">
         <v>364</v>
       </c>
-      <c r="G6" s="109" t="s">
-        <v>348</v>
+      <c r="G6" s="101">
+        <v>1938</v>
       </c>
       <c r="H6" s="109" t="s">
         <v>348</v>
       </c>
-      <c r="I6" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="J6" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="K6" s="107" t="s">
+      <c r="I6" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="J6" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="K6" s="109" t="s">
         <v>348</v>
       </c>
       <c r="L6" s="107" t="s">
@@ -4835,10 +4875,10 @@
       <c r="M6" s="107" t="s">
         <v>348</v>
       </c>
-      <c r="N6" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="O6" s="107" t="s">
+      <c r="N6" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="O6" s="108" t="s">
         <v>348</v>
       </c>
       <c r="P6" s="107" t="s">
@@ -4851,20 +4891,23 @@
         <v>348</v>
       </c>
       <c r="S6" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="T6" s="107" t="s">
         <v>349</v>
       </c>
-      <c r="T6" s="107" t="s">
-        <v>369</v>
-      </c>
       <c r="U6" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="V6" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="W6" s="106"/>
-    </row>
-    <row r="7" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>348</v>
+      </c>
+      <c r="V6" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="W6" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="X6" s="106"/>
+    </row>
+    <row r="7" spans="1:24" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="109" t="s">
         <v>129</v>
       </c>
@@ -4872,73 +4915,82 @@
         <v>80</v>
       </c>
       <c r="C7" s="109" t="s">
-        <v>123</v>
-      </c>
-      <c r="D7" s="114" t="s">
-        <v>104</v>
-      </c>
-      <c r="E7" s="114" t="s">
-        <v>362</v>
-      </c>
-      <c r="F7" s="114"/>
-      <c r="G7" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="H7" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="I7" s="111"/>
-      <c r="J7" s="113"/>
-      <c r="K7" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="L7" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="M7" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="N7" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="O7" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="P7" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q7" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="R7" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="S7" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="T7" s="113" t="s">
-        <v>348</v>
-      </c>
-      <c r="U7" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="V7" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="W7" s="106"/>
-    </row>
-    <row r="8" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="D7" s="101" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7" s="101" t="s">
+        <v>182</v>
+      </c>
+      <c r="F7" s="101" t="s">
+        <v>364</v>
+      </c>
+      <c r="G7" s="101">
+        <v>326</v>
+      </c>
+      <c r="H7" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="I7" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="J7" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="K7" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="L7" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="M7" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="N7" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="O7" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="P7" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q7" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="R7" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="S7" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="T7" s="107" t="s">
+        <v>349</v>
+      </c>
+      <c r="U7" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="V7" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="W7" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="X7" s="106"/>
+    </row>
+    <row r="8" spans="1:24" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="109" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="B8" s="110" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="108" t="s">
-        <v>368</v>
+      <c r="C8" s="109" t="s">
+        <v>126</v>
       </c>
       <c r="D8" s="101" t="s">
-        <v>366</v>
+        <v>113</v>
       </c>
       <c r="E8" s="101" t="s">
         <v>182</v>
@@ -4946,19 +4998,19 @@
       <c r="F8" s="101" t="s">
         <v>364</v>
       </c>
-      <c r="G8" s="109" t="s">
-        <v>348</v>
+      <c r="G8" s="101">
+        <v>1189</v>
       </c>
       <c r="H8" s="109" t="s">
         <v>348</v>
       </c>
-      <c r="I8" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="J8" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="K8" s="107" t="s">
+      <c r="I8" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="J8" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="K8" s="109" t="s">
         <v>348</v>
       </c>
       <c r="L8" s="107" t="s">
@@ -4967,10 +5019,10 @@
       <c r="M8" s="107" t="s">
         <v>348</v>
       </c>
-      <c r="N8" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="O8" s="107" t="s">
+      <c r="N8" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="O8" s="108" t="s">
         <v>348</v>
       </c>
       <c r="P8" s="107" t="s">
@@ -4983,169 +5035,176 @@
         <v>348</v>
       </c>
       <c r="S8" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="T8" s="107" t="s">
         <v>349</v>
       </c>
-      <c r="T8" s="107" t="s">
+      <c r="U8" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="V8" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="W8" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="X8" s="106"/>
+    </row>
+    <row r="9" spans="1:24" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="109" t="s">
+        <v>129</v>
+      </c>
+      <c r="B9" s="110" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="109" t="s">
+        <v>127</v>
+      </c>
+      <c r="D9" s="114" t="s">
+        <v>114</v>
+      </c>
+      <c r="E9" s="114" t="s">
+        <v>182</v>
+      </c>
+      <c r="F9" s="114" t="s">
+        <v>364</v>
+      </c>
+      <c r="G9" s="114">
+        <v>520</v>
+      </c>
+      <c r="H9" s="113" t="s">
+        <v>348</v>
+      </c>
+      <c r="I9" s="113" t="s">
+        <v>348</v>
+      </c>
+      <c r="J9" s="111"/>
+      <c r="K9" s="113"/>
+      <c r="L9" s="113" t="s">
+        <v>348</v>
+      </c>
+      <c r="M9" s="113" t="s">
+        <v>348</v>
+      </c>
+      <c r="N9" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="O9" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="113" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q9" s="113" t="s">
+        <v>348</v>
+      </c>
+      <c r="R9" s="113" t="s">
+        <v>348</v>
+      </c>
+      <c r="S9" s="113" t="s">
+        <v>348</v>
+      </c>
+      <c r="T9" s="113" t="s">
+        <v>347</v>
+      </c>
+      <c r="U9" s="113" t="s">
+        <v>347</v>
+      </c>
+      <c r="V9" s="113" t="s">
+        <v>347</v>
+      </c>
+      <c r="W9" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="X9" s="106" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="109" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" s="110" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="109" t="s">
+        <v>129</v>
+      </c>
+      <c r="D10" s="101" t="s">
+        <v>115</v>
+      </c>
+      <c r="E10" s="101" t="s">
+        <v>182</v>
+      </c>
+      <c r="F10" s="101" t="s">
+        <v>364</v>
+      </c>
+      <c r="G10" s="101">
+        <v>3482</v>
+      </c>
+      <c r="H10" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="I10" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="J10" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="K10" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="L10" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="M10" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="N10" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="O10" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="P10" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q10" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="R10" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="S10" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="T10" s="107" t="s">
+        <v>349</v>
+      </c>
+      <c r="U10" s="107" t="s">
         <v>369</v>
       </c>
-      <c r="U8" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="V8" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="W8" s="106"/>
-    </row>
-    <row r="9" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="109" t="s">
-        <v>132</v>
-      </c>
-      <c r="B9" s="110" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="108" t="s">
-        <v>132</v>
-      </c>
-      <c r="D9" s="101" t="s">
-        <v>116</v>
-      </c>
-      <c r="E9" s="124" t="s">
-        <v>235</v>
-      </c>
-      <c r="F9" s="124" t="s">
-        <v>364</v>
-      </c>
-      <c r="G9" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="H9" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="I9" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="J9" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="K9" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="L9" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="M9" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="N9" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="O9" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="P9" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="Q9" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="R9" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="S9" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="T9" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="U9" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="V9" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="W9" s="107"/>
-    </row>
-    <row r="10" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="109" t="s">
-        <v>132</v>
-      </c>
-      <c r="B10" s="110" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="108" t="s">
-        <v>132</v>
-      </c>
-      <c r="D10" s="101" t="s">
-        <v>117</v>
-      </c>
-      <c r="E10" s="124" t="s">
-        <v>238</v>
-      </c>
-      <c r="F10" s="124" t="s">
-        <v>364</v>
-      </c>
-      <c r="G10" s="115" t="s">
-        <v>348</v>
-      </c>
-      <c r="H10" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="I10" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="J10" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="K10" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="L10" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="M10" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="N10" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="O10" s="109" t="s">
-        <v>349</v>
-      </c>
-      <c r="P10" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="Q10" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="R10" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="S10" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="T10" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="U10" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="V10" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="W10" s="107"/>
-    </row>
-    <row r="11" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V10" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="W10" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="X10" s="107"/>
+    </row>
+    <row r="11" spans="1:24" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="109" t="s">
         <v>136</v>
       </c>
       <c r="B11" s="110" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="109" t="s">
-        <v>133</v>
+        <v>80</v>
+      </c>
+      <c r="C11" s="108" t="s">
+        <v>368</v>
       </c>
       <c r="D11" s="101" t="s">
-        <v>118</v>
+        <v>366</v>
       </c>
       <c r="E11" s="101" t="s">
         <v>182</v>
@@ -5153,137 +5212,143 @@
       <c r="F11" s="101" t="s">
         <v>364</v>
       </c>
-      <c r="G11" s="115" t="s">
-        <v>348</v>
-      </c>
-      <c r="H11" s="113" t="s">
-        <v>348</v>
-      </c>
-      <c r="I11" s="111" t="s">
-        <v>348</v>
-      </c>
-      <c r="J11" s="113" t="s">
-        <v>348</v>
-      </c>
-      <c r="K11" s="111" t="s">
-        <v>348</v>
-      </c>
-      <c r="L11" s="111" t="s">
-        <v>348</v>
-      </c>
-      <c r="M11" s="111" t="s">
-        <v>348</v>
-      </c>
-      <c r="N11" s="112" t="s">
-        <v>348</v>
-      </c>
-      <c r="O11" s="111" t="s">
-        <v>348</v>
-      </c>
-      <c r="P11" s="111" t="s">
-        <v>347</v>
-      </c>
-      <c r="Q11" s="111" t="s">
-        <v>348</v>
-      </c>
-      <c r="R11" s="111" t="s">
-        <v>347</v>
-      </c>
-      <c r="S11" s="111" t="s">
-        <v>347</v>
-      </c>
-      <c r="T11" s="111" t="s">
+      <c r="G11" s="101">
+        <v>1496</v>
+      </c>
+      <c r="H11" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="I11" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="J11" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="K11" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="L11" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="M11" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="N11" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="O11" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="P11" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q11" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="R11" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="S11" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="T11" s="107" t="s">
+        <v>349</v>
+      </c>
+      <c r="U11" s="107" t="s">
         <v>369</v>
       </c>
-      <c r="U11" s="111" t="s">
-        <v>347</v>
-      </c>
-      <c r="V11" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="W11" s="106"/>
-    </row>
-    <row r="12" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V11" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="W11" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="X11" s="106"/>
+    </row>
+    <row r="12" spans="1:24" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="109" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B12" s="110" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="C12" s="109" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D12" s="101" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E12" s="101" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="F12" s="101" t="s">
         <v>364</v>
       </c>
-      <c r="G12" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="H12" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="I12" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="J12" s="116" t="s">
-        <v>348</v>
-      </c>
-      <c r="K12" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="L12" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="M12" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="N12" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="O12" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="P12" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="Q12" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="R12" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="S12" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="T12" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="U12" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="V12" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="W12" s="106"/>
-    </row>
-    <row r="13" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G12" s="101">
+        <v>1090</v>
+      </c>
+      <c r="H12" s="115" t="s">
+        <v>348</v>
+      </c>
+      <c r="I12" s="113" t="s">
+        <v>348</v>
+      </c>
+      <c r="J12" s="111" t="s">
+        <v>348</v>
+      </c>
+      <c r="K12" s="113" t="s">
+        <v>348</v>
+      </c>
+      <c r="L12" s="111" t="s">
+        <v>348</v>
+      </c>
+      <c r="M12" s="111" t="s">
+        <v>348</v>
+      </c>
+      <c r="N12" s="111" t="s">
+        <v>348</v>
+      </c>
+      <c r="O12" s="112" t="s">
+        <v>348</v>
+      </c>
+      <c r="P12" s="111" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q12" s="111" t="s">
+        <v>347</v>
+      </c>
+      <c r="R12" s="111" t="s">
+        <v>348</v>
+      </c>
+      <c r="S12" s="111" t="s">
+        <v>347</v>
+      </c>
+      <c r="T12" s="111" t="s">
+        <v>347</v>
+      </c>
+      <c r="U12" s="111" t="s">
+        <v>369</v>
+      </c>
+      <c r="V12" s="111" t="s">
+        <v>347</v>
+      </c>
+      <c r="W12" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="X12" s="106"/>
+    </row>
+    <row r="13" spans="1:24" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="109" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B13" s="110" t="s">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C13" s="109" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D13" s="101" t="s">
-        <v>28</v>
+        <v>119</v>
       </c>
       <c r="E13" s="101" t="s">
         <v>169</v>
@@ -5291,19 +5356,19 @@
       <c r="F13" s="101" t="s">
         <v>364</v>
       </c>
-      <c r="G13" s="109" t="s">
-        <v>348</v>
+      <c r="G13" s="128">
+        <v>408</v>
       </c>
       <c r="H13" s="109" t="s">
         <v>348</v>
       </c>
-      <c r="I13" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="J13" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="K13" s="107" t="s">
+      <c r="I13" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="J13" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="K13" s="109" t="s">
         <v>348</v>
       </c>
       <c r="L13" s="107" t="s">
@@ -5312,294 +5377,327 @@
       <c r="M13" s="107" t="s">
         <v>348</v>
       </c>
-      <c r="N13" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="O13" s="107" t="s">
+      <c r="N13" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="O13" s="108" t="s">
         <v>348</v>
       </c>
       <c r="P13" s="107" t="s">
         <v>348</v>
       </c>
       <c r="Q13" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="R13" s="107" t="s">
         <v>348</v>
       </c>
       <c r="S13" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="T13" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="U13" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="V13" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="W13" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="X13" s="106"/>
+    </row>
+    <row r="14" spans="1:24" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="109" t="s">
+        <v>132</v>
+      </c>
+      <c r="B14" s="110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="109" t="s">
+        <v>130</v>
+      </c>
+      <c r="D14" s="101" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="101" t="s">
+        <v>182</v>
+      </c>
+      <c r="F14" s="101" t="s">
+        <v>364</v>
+      </c>
+      <c r="G14" s="128">
+        <v>315</v>
+      </c>
+      <c r="H14" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="I14" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="J14" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="K14" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="L14" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="M14" s="107" t="s">
         <v>349</v>
       </c>
-      <c r="T13" s="107" t="s">
+      <c r="N14" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="O14" s="108" t="s">
+        <v>347</v>
+      </c>
+      <c r="P14" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q14" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="R14" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="S14" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="T14" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="U14" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="V14" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="W14" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="X14" s="107"/>
+    </row>
+    <row r="15" spans="1:24" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="109" t="s">
+        <v>132</v>
+      </c>
+      <c r="B15" s="110" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="108" t="s">
+        <v>132</v>
+      </c>
+      <c r="D15" s="101" t="s">
+        <v>116</v>
+      </c>
+      <c r="E15" s="124" t="s">
+        <v>235</v>
+      </c>
+      <c r="F15" s="124" t="s">
+        <v>364</v>
+      </c>
+      <c r="G15" s="129">
+        <v>513</v>
+      </c>
+      <c r="H15" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="I15" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="J15" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="K15" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="L15" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="M15" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="N15" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="O15" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="P15" s="107" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q15" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="R15" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="S15" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="T15" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="U15" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="V15" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="W15" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="X15" s="107"/>
+    </row>
+    <row r="16" spans="1:24" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="109" t="s">
+        <v>132</v>
+      </c>
+      <c r="B16" s="110" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="108" t="s">
+        <v>132</v>
+      </c>
+      <c r="D16" s="101" t="s">
+        <v>117</v>
+      </c>
+      <c r="E16" s="124" t="s">
+        <v>238</v>
+      </c>
+      <c r="F16" s="124" t="s">
+        <v>364</v>
+      </c>
+      <c r="G16" s="129">
         <v>369</v>
       </c>
-      <c r="U13" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="V13" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="W13" s="106"/>
-    </row>
-    <row r="14" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="109" t="s">
-        <v>129</v>
-      </c>
-      <c r="B14" s="110" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="109" t="s">
-        <v>124</v>
-      </c>
-      <c r="D14" s="114" t="s">
-        <v>106</v>
-      </c>
-      <c r="E14" s="114" t="s">
-        <v>196</v>
-      </c>
-      <c r="F14" s="114"/>
-      <c r="G14" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="H14" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="111"/>
-      <c r="J14" s="113"/>
-      <c r="K14" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="L14" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="M14" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="N14" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="O14" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="P14" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q14" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="R14" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="S14" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="T14" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="U14" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="V14" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="W14" s="106"/>
-    </row>
-    <row r="15" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="109" t="s">
-        <v>129</v>
-      </c>
-      <c r="B15" s="110" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="109" t="s">
-        <v>124</v>
-      </c>
-      <c r="D15" s="114" t="s">
-        <v>105</v>
-      </c>
-      <c r="E15" s="114" t="s">
-        <v>200</v>
-      </c>
-      <c r="F15" s="114"/>
-      <c r="G15" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="H15" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="I15" s="111"/>
-      <c r="J15" s="113"/>
-      <c r="K15" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="L15" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="M15" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="N15" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="O15" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="P15" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q15" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="R15" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="S15" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="T15" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="U15" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="V15" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="W15" s="106"/>
-    </row>
-    <row r="16" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="109" t="s">
-        <v>129</v>
-      </c>
-      <c r="B16" s="110" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" s="109" t="s">
-        <v>128</v>
-      </c>
-      <c r="D16" s="114" t="s">
-        <v>92</v>
-      </c>
-      <c r="E16" s="114" t="s">
-        <v>317</v>
-      </c>
-      <c r="F16" s="114"/>
-      <c r="G16" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="H16" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="I16" s="111"/>
-      <c r="J16" s="113"/>
-      <c r="K16" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="L16" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="M16" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="N16" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="O16" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="P16" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q16" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="R16" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="S16" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="T16" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="U16" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="V16" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="W16" s="106"/>
-    </row>
-    <row r="17" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H16" s="115" t="s">
+        <v>348</v>
+      </c>
+      <c r="I16" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="J16" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="K16" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="L16" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="M16" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="N16" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="O16" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="P16" s="109" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q16" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="R16" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="S16" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="T16" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="U16" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="V16" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="W16" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="X16" s="107"/>
+    </row>
+    <row r="17" spans="1:24" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="109" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B17" s="110" t="s">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="C17" s="109" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D17" s="101" t="s">
-        <v>109</v>
+        <v>346</v>
       </c>
       <c r="E17" s="101" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="F17" s="101" t="s">
         <v>364</v>
       </c>
-      <c r="G17" s="109" t="s">
-        <v>348</v>
+      <c r="G17" s="101">
+        <v>1403</v>
       </c>
       <c r="H17" s="109" t="s">
         <v>348</v>
       </c>
-      <c r="I17" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="J17" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="K17" s="107" t="s">
+      <c r="I17" s="109" t="s">
+        <v>148</v>
+      </c>
+      <c r="J17" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="K17" s="109" t="s">
         <v>348</v>
       </c>
       <c r="L17" s="107" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M17" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="N17" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="O17" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
+      </c>
+      <c r="N17" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="O17" s="108" t="s">
+        <v>347</v>
       </c>
       <c r="P17" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q17" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="R17" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="S17" s="107" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="T17" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="U17" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="V17" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="W17" s="106"/>
-    </row>
-    <row r="18" spans="1:23" s="103" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+      <c r="V17" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="W17" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="X17" s="107"/>
+    </row>
+    <row r="18" spans="1:24" s="103" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="109" t="s">
         <v>129</v>
       </c>
@@ -5607,28 +5705,26 @@
         <v>80</v>
       </c>
       <c r="C18" s="109" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D18" s="101" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E18" s="101" t="s">
-        <v>314</v>
+        <v>196</v>
       </c>
       <c r="F18" s="101"/>
-      <c r="G18" s="109" t="s">
-        <v>348</v>
-      </c>
+      <c r="G18" s="101"/>
       <c r="H18" s="109" t="s">
         <v>348</v>
       </c>
-      <c r="I18" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="J18" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="K18" s="107" t="s">
+      <c r="I18" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="J18" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="K18" s="109" t="s">
         <v>348</v>
       </c>
       <c r="L18" s="107" t="s">
@@ -5637,36 +5733,39 @@
       <c r="M18" s="107" t="s">
         <v>348</v>
       </c>
-      <c r="N18" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="O18" s="107" t="s">
+      <c r="N18" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="O18" s="108" t="s">
         <v>348</v>
       </c>
       <c r="P18" s="107" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q18" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="R18" s="107" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="S18" s="107" t="s">
         <v>347</v>
       </c>
       <c r="T18" s="107" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
       <c r="U18" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="V18" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="W18" s="106"/>
-    </row>
-    <row r="19" spans="1:23" s="103" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>348</v>
+      </c>
+      <c r="V18" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="W18" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="X18" s="106"/>
+    </row>
+    <row r="19" spans="1:24" s="103" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="109" t="s">
         <v>129</v>
       </c>
@@ -5674,30 +5773,26 @@
         <v>80</v>
       </c>
       <c r="C19" s="109" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D19" s="101" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E19" s="101" t="s">
-        <v>182</v>
-      </c>
-      <c r="F19" s="101" t="s">
-        <v>364</v>
-      </c>
-      <c r="G19" s="109" t="s">
-        <v>348</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="F19" s="101"/>
+      <c r="G19" s="101"/>
       <c r="H19" s="109" t="s">
         <v>348</v>
       </c>
-      <c r="I19" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="J19" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="K19" s="107" t="s">
+      <c r="I19" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="J19" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="K19" s="109" t="s">
         <v>348</v>
       </c>
       <c r="L19" s="107" t="s">
@@ -5706,10 +5801,10 @@
       <c r="M19" s="107" t="s">
         <v>348</v>
       </c>
-      <c r="N19" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="O19" s="107" t="s">
+      <c r="N19" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="O19" s="108" t="s">
         <v>348</v>
       </c>
       <c r="P19" s="107" t="s">
@@ -5719,23 +5814,26 @@
         <v>348</v>
       </c>
       <c r="R19" s="107" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="S19" s="107" t="s">
         <v>349</v>
       </c>
       <c r="T19" s="107" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="U19" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="V19" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="W19" s="106"/>
-    </row>
-    <row r="20" spans="1:23" s="103" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+      <c r="V19" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="W19" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="X19" s="106"/>
+    </row>
+    <row r="20" spans="1:24" s="103" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="109" t="s">
         <v>129</v>
       </c>
@@ -5743,26 +5841,24 @@
         <v>80</v>
       </c>
       <c r="C20" s="109" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D20" s="114" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E20" s="114" t="s">
-        <v>329</v>
+        <v>362</v>
       </c>
       <c r="F20" s="114"/>
-      <c r="G20" s="113" t="s">
-        <v>5</v>
-      </c>
+      <c r="G20" s="114"/>
       <c r="H20" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="I20" s="111"/>
-      <c r="J20" s="113"/>
-      <c r="K20" s="113" t="s">
-        <v>5</v>
-      </c>
+      <c r="I20" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="111"/>
+      <c r="K20" s="113"/>
       <c r="L20" s="113" t="s">
         <v>5</v>
       </c>
@@ -5788,184 +5884,175 @@
         <v>5</v>
       </c>
       <c r="T20" s="113" t="s">
-        <v>348</v>
+        <v>5</v>
       </c>
       <c r="U20" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="V20" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="W20" s="106"/>
-    </row>
-    <row r="21" spans="1:23" s="103" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>348</v>
+      </c>
+      <c r="V20" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="W20" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="X20" s="106"/>
+    </row>
+    <row r="21" spans="1:24" s="103" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="109" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="B21" s="110" t="s">
-        <v>3</v>
-      </c>
-      <c r="C21" s="108" t="s">
-        <v>134</v>
-      </c>
-      <c r="D21" s="101" t="s">
-        <v>120</v>
-      </c>
-      <c r="E21" s="101" t="s">
-        <v>174</v>
-      </c>
-      <c r="F21" s="101"/>
-      <c r="G21" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="H21" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="I21" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="J21" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="K21" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="L21" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="M21" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="N21" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="O21" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="P21" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="Q21" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="R21" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="S21" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="T21" s="107" t="s">
-        <v>369</v>
-      </c>
-      <c r="U21" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="V21" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="W21" s="106"/>
-    </row>
-    <row r="22" spans="1:23" s="103" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="C21" s="109" t="s">
+        <v>124</v>
+      </c>
+      <c r="D21" s="114" t="s">
+        <v>106</v>
+      </c>
+      <c r="E21" s="114" t="s">
+        <v>196</v>
+      </c>
+      <c r="F21" s="114"/>
+      <c r="G21" s="114"/>
+      <c r="H21" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="I21" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="J21" s="111"/>
+      <c r="K21" s="113"/>
+      <c r="L21" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="M21" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="N21" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="O21" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="S21" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="U21" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="V21" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="W21" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="X21" s="106"/>
+    </row>
+    <row r="22" spans="1:24" s="103" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="109" t="s">
         <v>129</v>
       </c>
       <c r="B22" s="110" t="s">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="C22" s="109" t="s">
-        <v>126</v>
-      </c>
-      <c r="D22" s="101" t="s">
-        <v>113</v>
-      </c>
-      <c r="E22" s="101" t="s">
-        <v>182</v>
-      </c>
-      <c r="F22" s="101" t="s">
-        <v>364</v>
-      </c>
-      <c r="G22" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="H22" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="I22" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="J22" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="K22" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="L22" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="M22" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="N22" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="O22" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="P22" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="Q22" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="R22" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="S22" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="T22" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="U22" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="V22" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="W22" s="106"/>
-    </row>
-    <row r="23" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+      <c r="D22" s="114" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22" s="114" t="s">
+        <v>200</v>
+      </c>
+      <c r="F22" s="114"/>
+      <c r="G22" s="114"/>
+      <c r="H22" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="111"/>
+      <c r="K22" s="113"/>
+      <c r="L22" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="M22" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="N22" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="O22" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="P22" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="R22" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="S22" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="T22" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="U22" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="V22" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="W22" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="X22" s="106"/>
+    </row>
+    <row r="23" spans="1:24" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="109" t="s">
         <v>129</v>
       </c>
       <c r="B23" s="110" t="s">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="C23" s="109" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D23" s="114" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="E23" s="114" t="s">
-        <v>182</v>
-      </c>
-      <c r="F23" s="114" t="s">
-        <v>364</v>
-      </c>
-      <c r="G23" s="113" t="s">
-        <v>348</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="F23" s="114"/>
+      <c r="G23" s="114"/>
       <c r="H23" s="113" t="s">
-        <v>348</v>
-      </c>
-      <c r="I23" s="111"/>
-      <c r="J23" s="113"/>
-      <c r="K23" s="113" t="s">
-        <v>348</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="I23" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="J23" s="111"/>
+      <c r="K23" s="113"/>
       <c r="L23" s="113" t="s">
-        <v>348</v>
+        <v>5</v>
       </c>
       <c r="M23" s="113" t="s">
         <v>5</v>
@@ -5974,65 +6061,62 @@
         <v>5</v>
       </c>
       <c r="O23" s="113" t="s">
-        <v>348</v>
+        <v>5</v>
       </c>
       <c r="P23" s="113" t="s">
-        <v>348</v>
+        <v>5</v>
       </c>
       <c r="Q23" s="113" t="s">
-        <v>348</v>
+        <v>5</v>
       </c>
       <c r="R23" s="113" t="s">
-        <v>348</v>
+        <v>5</v>
       </c>
       <c r="S23" s="113" t="s">
-        <v>347</v>
+        <v>5</v>
       </c>
       <c r="T23" s="113" t="s">
-        <v>347</v>
+        <v>5</v>
       </c>
       <c r="U23" s="113" t="s">
-        <v>347</v>
-      </c>
-      <c r="V23" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="W23" s="106" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="V23" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="W23" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="X23" s="106"/>
+    </row>
+    <row r="24" spans="1:24" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="109" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="B24" s="110" t="s">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C24" s="109" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="D24" s="101" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="E24" s="101" t="s">
-        <v>169</v>
-      </c>
-      <c r="F24" s="101" t="s">
-        <v>364</v>
-      </c>
-      <c r="G24" s="109" t="s">
-        <v>348</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="F24" s="101"/>
+      <c r="G24" s="101"/>
       <c r="H24" s="109" t="s">
         <v>348</v>
       </c>
-      <c r="I24" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="J24" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="K24" s="107" t="s">
+      <c r="I24" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="J24" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="K24" s="109" t="s">
         <v>348</v>
       </c>
       <c r="L24" s="107" t="s">
@@ -6041,36 +6125,39 @@
       <c r="M24" s="107" t="s">
         <v>348</v>
       </c>
-      <c r="N24" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="O24" s="107" t="s">
+      <c r="N24" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="O24" s="108" t="s">
         <v>348</v>
       </c>
       <c r="P24" s="107" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q24" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="R24" s="107" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="S24" s="107" t="s">
         <v>347</v>
       </c>
       <c r="T24" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="U24" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="V24" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="W24" s="106"/>
-    </row>
-    <row r="25" spans="1:23" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+      <c r="V24" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="W24" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="X24" s="106"/>
+    </row>
+    <row r="25" spans="1:24" s="105" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="109" t="s">
         <v>129</v>
       </c>
@@ -6081,229 +6168,228 @@
         <v>126</v>
       </c>
       <c r="D25" s="114" t="s">
+        <v>112</v>
+      </c>
+      <c r="E25" s="114" t="s">
+        <v>329</v>
+      </c>
+      <c r="F25" s="114"/>
+      <c r="G25" s="114"/>
+      <c r="H25" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="I25" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="J25" s="111"/>
+      <c r="K25" s="113"/>
+      <c r="L25" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="M25" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="N25" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="O25" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="P25" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q25" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="R25" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="S25" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="T25" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="U25" s="113" t="s">
+        <v>348</v>
+      </c>
+      <c r="V25" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="W25" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="X25" s="106"/>
+    </row>
+    <row r="26" spans="1:24" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="109" t="s">
+        <v>136</v>
+      </c>
+      <c r="B26" s="110" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="108" t="s">
+        <v>134</v>
+      </c>
+      <c r="D26" s="101" t="s">
+        <v>120</v>
+      </c>
+      <c r="E26" s="101" t="s">
+        <v>174</v>
+      </c>
+      <c r="F26" s="101"/>
+      <c r="G26" s="101"/>
+      <c r="H26" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="I26" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="J26" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="K26" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="L26" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="M26" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="N26" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="O26" s="108" t="s">
+        <v>348</v>
+      </c>
+      <c r="P26" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q26" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="R26" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="S26" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="T26" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="U26" s="107" t="s">
+        <v>369</v>
+      </c>
+      <c r="V26" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="W26" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="X26" s="106"/>
+    </row>
+    <row r="27" spans="1:24" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="109" t="s">
+        <v>129</v>
+      </c>
+      <c r="B27" s="110" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="109" t="s">
+        <v>126</v>
+      </c>
+      <c r="D27" s="114" t="s">
         <v>111</v>
       </c>
-      <c r="E25" s="114" t="s">
+      <c r="E27" s="114" t="s">
         <v>363</v>
       </c>
-      <c r="F25" s="114"/>
-      <c r="G25" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="H25" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="I25" s="111"/>
-      <c r="J25" s="113"/>
-      <c r="K25" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="L25" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="M25" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="N25" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="O25" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="P25" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q25" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="R25" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="S25" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="T25" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="U25" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="V25" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="W25" s="106"/>
-    </row>
-    <row r="26" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="109" t="s">
-        <v>129</v>
-      </c>
-      <c r="B26" s="110" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" s="109" t="s">
-        <v>129</v>
-      </c>
-      <c r="D26" s="101" t="s">
-        <v>115</v>
-      </c>
-      <c r="E26" s="101" t="s">
-        <v>182</v>
-      </c>
-      <c r="F26" s="101" t="s">
-        <v>364</v>
-      </c>
-      <c r="G26" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="H26" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="I26" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="J26" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="K26" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="L26" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="M26" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="N26" s="108" t="s">
-        <v>348</v>
-      </c>
-      <c r="O26" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="P26" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="Q26" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="R26" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="S26" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="T26" s="107" t="s">
-        <v>369</v>
-      </c>
-      <c r="U26" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="V26" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="W26" s="107"/>
-    </row>
-    <row r="27" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="109" t="s">
-        <v>132</v>
-      </c>
-      <c r="B27" s="110" t="s">
-        <v>137</v>
-      </c>
-      <c r="C27" s="109" t="s">
-        <v>131</v>
-      </c>
-      <c r="D27" s="101" t="s">
-        <v>346</v>
-      </c>
-      <c r="E27" s="101" t="s">
-        <v>213</v>
-      </c>
-      <c r="F27" s="101" t="s">
-        <v>364</v>
-      </c>
-      <c r="G27" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="H27" s="109" t="s">
-        <v>148</v>
-      </c>
-      <c r="I27" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="J27" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="K27" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="L27" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="M27" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="N27" s="108" t="s">
-        <v>347</v>
-      </c>
-      <c r="O27" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="P27" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="Q27" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="R27" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="S27" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="T27" s="107" t="s">
-        <v>369</v>
-      </c>
-      <c r="U27" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="V27" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="W27" s="107"/>
+      <c r="F27" s="114"/>
+      <c r="G27" s="114"/>
+      <c r="H27" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="I27" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="J27" s="111"/>
+      <c r="K27" s="113"/>
+      <c r="L27" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="M27" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="N27" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="O27" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="P27" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="R27" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="S27" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="T27" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="U27" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="V27" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="W27" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="X27" s="106"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W27" xr:uid="{ED25CF60-E519-46A5-8820-1361CFDEEEDA}"/>
-  <conditionalFormatting sqref="G2:U27">
+  <autoFilter ref="A1:X27" xr:uid="{ED25CF60-E519-46A5-8820-1361CFDEEEDA}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X17">
+      <sortCondition descending="1" ref="A1:A27"/>
+    </sortState>
+  </autoFilter>
+  <conditionalFormatting sqref="H2:V27">
     <cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="Planned">
-      <formula>NOT(ISERROR(SEARCH("Planned",G2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Planned",H2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="19" priority="2" operator="containsText" text="Imputation">
-      <formula>NOT(ISERROR(SEARCH("Imputation",G2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Imputation",H2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="18" priority="3" operator="containsText" text="Not Applicable">
-      <formula>NOT(ISERROR(SEARCH("Not Applicable",G2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Not Applicable",H2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="17" priority="4" operator="containsText" text="Completed">
-      <formula>NOT(ISERROR(SEARCH("Completed",G2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Completed",H2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="Ongoing">
-      <formula>NOT(ISERROR(SEARCH("Ongoing",G2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Ongoing",H2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="15" priority="6" operator="containsText" text="Not started">
-      <formula>NOT(ISERROR(SEARCH("Not started",G2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Not started",H2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5" xr:uid="{6808D71E-5544-43A0-9FB9-83F708D369A7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5" xr:uid="{6808D71E-5544-43A0-9FB9-83F708D369A7}">
       <formula1>"Completed, Ongoing,Not started,Not Applicable,Unknown"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N8" xr:uid="{2B9F2373-149C-4DF6-A36F-56BDABEF16A1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O8" xr:uid="{2B9F2373-149C-4DF6-A36F-56BDABEF16A1}">
       <formula1>"Completed, Ongoing,Not started,Not Applicable "</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H4 H6:H27 K2:U7 G2:G27 I2:J27 O8:U27 K8:M27 N9:N27" xr:uid="{8254B028-7BD1-41C2-836F-FB15DD3907FA}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I4 I6:I27 L2:V7 H2:H27 J2:K27 P8:V27 L8:N27 O9:O27" xr:uid="{8254B028-7BD1-41C2-836F-FB15DD3907FA}">
       <formula1>"Completed, Ongoing,Not started,Not Applicable,Unknown,Done,Planned"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" promptTitle="Status" prompt="Pick a status" sqref="W2:W27" xr:uid="{5ABEEBC5-EE20-4A05-A73F-52A631225389}"/>
+    <dataValidation allowBlank="1" promptTitle="Status" prompt="Pick a status" sqref="X2:X27" xr:uid="{5ABEEBC5-EE20-4A05-A73F-52A631225389}"/>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/clic_data.xlsx
+++ b/clic_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luxxx371\Box\Requests\Clic\Administration\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDEB4527-E162-494F-93AE-23F75316D6A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20C16CA-BDFF-4A00-A6BC-6AA09D2908AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Total Studies" sheetId="8" r:id="rId1"/>
@@ -1116,9 +1116,6 @@
     <t>Ongoing</t>
   </si>
   <si>
-    <t xml:space="preserve">Aim 3 EPI Data Data Avaliability </t>
-  </si>
-  <si>
     <t>RFMIx</t>
   </si>
   <si>
@@ -1192,6 +1189,9 @@
   </si>
   <si>
     <t>Proposed Cases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aim 3 EPI Data Avaliability </t>
   </si>
 </sst>
 </file>
@@ -3558,13 +3558,13 @@
         <v>32</v>
       </c>
       <c r="D31" s="70" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E31" s="19" t="s">
         <v>169</v>
       </c>
       <c r="F31" s="127" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G31" s="74" t="s">
         <v>229</v>
@@ -3573,7 +3573,7 @@
         <v>5</v>
       </c>
       <c r="I31" s="70" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4297,7 +4297,7 @@
   <sheetData>
     <row r="1" spans="1:13" s="11" customFormat="1" ht="63" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>0</v>
@@ -4487,31 +4487,31 @@
         <v>100</v>
       </c>
       <c r="E1" s="123" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F1" s="123" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G1" s="123" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1" s="119" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="I1" s="118" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J1" s="26" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K1" s="26" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="L1" s="117" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="M1" s="117" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="N1" s="26" t="s">
         <v>341</v>
@@ -4523,25 +4523,25 @@
         <v>342</v>
       </c>
       <c r="Q1" s="117" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="R1" s="117" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="S1" s="117" t="s">
         <v>155</v>
       </c>
       <c r="T1" s="117" t="s">
+        <v>372</v>
+      </c>
+      <c r="U1" s="117" t="s">
         <v>373</v>
-      </c>
-      <c r="U1" s="117" t="s">
-        <v>374</v>
       </c>
       <c r="V1" s="117" t="s">
         <v>99</v>
       </c>
       <c r="W1" s="117" t="s">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="X1" s="26" t="s">
         <v>2</v>
@@ -4564,7 +4564,7 @@
         <v>169</v>
       </c>
       <c r="F2" s="101" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G2" s="129">
         <v>1692</v>
@@ -4609,7 +4609,7 @@
         <v>349</v>
       </c>
       <c r="U2" s="107" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="V2" s="107" t="s">
         <v>347</v>
@@ -4627,16 +4627,16 @@
         <v>80</v>
       </c>
       <c r="C3" s="108" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D3" s="124" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E3" s="101" t="s">
         <v>182</v>
       </c>
       <c r="F3" s="101" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G3" s="101">
         <v>3834</v>
@@ -4681,7 +4681,7 @@
         <v>349</v>
       </c>
       <c r="U3" s="107" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="V3" s="107" t="s">
         <v>347</v>
@@ -4708,7 +4708,7 @@
         <v>169</v>
       </c>
       <c r="F4" s="101" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G4" s="101">
         <v>1125</v>
@@ -4780,7 +4780,7 @@
         <v>169</v>
       </c>
       <c r="F5" s="101" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G5" s="101">
         <v>45</v>
@@ -4825,7 +4825,7 @@
         <v>349</v>
       </c>
       <c r="U5" s="107" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="V5" s="107" t="s">
         <v>347</v>
@@ -4852,7 +4852,7 @@
         <v>182</v>
       </c>
       <c r="F6" s="101" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G6" s="101">
         <v>1938</v>
@@ -4924,7 +4924,7 @@
         <v>182</v>
       </c>
       <c r="F7" s="101" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G7" s="101">
         <v>326</v>
@@ -4996,7 +4996,7 @@
         <v>182</v>
       </c>
       <c r="F8" s="101" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G8" s="101">
         <v>1189</v>
@@ -5068,7 +5068,7 @@
         <v>182</v>
       </c>
       <c r="F9" s="114" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G9" s="114">
         <v>520</v>
@@ -5138,7 +5138,7 @@
         <v>182</v>
       </c>
       <c r="F10" s="101" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G10" s="101">
         <v>3482</v>
@@ -5183,7 +5183,7 @@
         <v>349</v>
       </c>
       <c r="U10" s="107" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="V10" s="107" t="s">
         <v>347</v>
@@ -5201,16 +5201,16 @@
         <v>80</v>
       </c>
       <c r="C11" s="108" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D11" s="101" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E11" s="101" t="s">
         <v>182</v>
       </c>
       <c r="F11" s="101" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G11" s="101">
         <v>1496</v>
@@ -5255,7 +5255,7 @@
         <v>349</v>
       </c>
       <c r="U11" s="107" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="V11" s="107" t="s">
         <v>347</v>
@@ -5282,7 +5282,7 @@
         <v>182</v>
       </c>
       <c r="F12" s="101" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G12" s="101">
         <v>1090</v>
@@ -5327,7 +5327,7 @@
         <v>347</v>
       </c>
       <c r="U12" s="111" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="V12" s="111" t="s">
         <v>347</v>
@@ -5354,7 +5354,7 @@
         <v>169</v>
       </c>
       <c r="F13" s="101" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G13" s="128">
         <v>408</v>
@@ -5426,7 +5426,7 @@
         <v>182</v>
       </c>
       <c r="F14" s="101" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G14" s="128">
         <v>315</v>
@@ -5498,7 +5498,7 @@
         <v>235</v>
       </c>
       <c r="F15" s="124" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G15" s="129">
         <v>513</v>
@@ -5570,7 +5570,7 @@
         <v>238</v>
       </c>
       <c r="F16" s="124" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G16" s="129">
         <v>369</v>
@@ -5642,7 +5642,7 @@
         <v>213</v>
       </c>
       <c r="F17" s="101" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G17" s="101">
         <v>1403</v>
@@ -5687,7 +5687,7 @@
         <v>347</v>
       </c>
       <c r="U17" s="107" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="V17" s="107" t="s">
         <v>347</v>
@@ -5823,7 +5823,7 @@
         <v>349</v>
       </c>
       <c r="U19" s="107" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="V19" s="107" t="s">
         <v>347</v>
@@ -5847,7 +5847,7 @@
         <v>104</v>
       </c>
       <c r="E20" s="114" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F20" s="114"/>
       <c r="G20" s="114"/>
@@ -6147,7 +6147,7 @@
         <v>347</v>
       </c>
       <c r="U24" s="107" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="V24" s="107" t="s">
         <v>347</v>
@@ -6279,7 +6279,7 @@
         <v>347</v>
       </c>
       <c r="U26" s="107" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="V26" s="107" t="s">
         <v>347</v>
@@ -6303,7 +6303,7 @@
         <v>111</v>
       </c>
       <c r="E27" s="114" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F27" s="114"/>
       <c r="G27" s="114"/>
@@ -8451,7 +8451,7 @@
         <v>53</v>
       </c>
       <c r="I3" s="120" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J3" s="4"/>
     </row>
@@ -8541,7 +8541,7 @@
         <v>53</v>
       </c>
       <c r="I6" s="120" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J6" s="4"/>
     </row>
@@ -8562,7 +8562,7 @@
         <v>53</v>
       </c>
       <c r="F7" s="120" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G7" s="120" t="s">
         <v>148</v>
@@ -8601,7 +8601,7 @@
         <v>53</v>
       </c>
       <c r="I8" s="120" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J8" s="4"/>
     </row>
@@ -8661,7 +8661,7 @@
         <v>53</v>
       </c>
       <c r="I10" s="120" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J10" s="4"/>
     </row>
@@ -8691,7 +8691,7 @@
         <v>53</v>
       </c>
       <c r="I11" s="120" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J11" s="4"/>
     </row>
@@ -8706,13 +8706,13 @@
         <v>53</v>
       </c>
       <c r="D12" s="120" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E12" s="120" t="s">
         <v>54</v>
       </c>
       <c r="F12" s="120" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G12" s="120" t="s">
         <v>148</v>
@@ -8721,7 +8721,7 @@
         <v>53</v>
       </c>
       <c r="I12" s="120" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J12" s="4"/>
     </row>
@@ -8742,16 +8742,16 @@
         <v>54</v>
       </c>
       <c r="F13" s="120" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G13" s="120" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H13" s="120" t="s">
         <v>53</v>
       </c>
       <c r="I13" s="120" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -8803,7 +8803,7 @@
         <v>54</v>
       </c>
       <c r="F15" s="120" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G15" s="120" t="s">
         <v>148</v>
@@ -8812,7 +8812,7 @@
         <v>53</v>
       </c>
       <c r="I15" s="120" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>20</v>
@@ -8964,7 +8964,7 @@
         <v>53</v>
       </c>
       <c r="I20" s="120" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J20" s="4"/>
     </row>
@@ -9191,22 +9191,22 @@
         <v>53</v>
       </c>
       <c r="D28" s="120" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E28" s="120" t="s">
         <v>54</v>
       </c>
       <c r="F28" s="120" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G28" s="120" t="s">
         <v>148</v>
       </c>
       <c r="H28" s="120" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="I28" s="120" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J28" s="4"/>
     </row>
@@ -9357,7 +9357,7 @@
         <v>53</v>
       </c>
       <c r="I33" s="120" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J33" s="4"/>
     </row>
@@ -9798,10 +9798,10 @@
         <v>148</v>
       </c>
       <c r="H48" s="120" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="I48" s="120" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">

--- a/clic_data.xlsx
+++ b/clic_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luxxx371\Box\Requests\Clic\Administration\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20C16CA-BDFF-4A00-A6BC-6AA09D2908AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0BB21F1-2BF0-434D-A2A5-374C50F8614C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5447,25 +5447,25 @@
         <v>348</v>
       </c>
       <c r="M14" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="N14" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="O14" s="108" t="s">
+        <v>347</v>
+      </c>
+      <c r="P14" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q14" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="R14" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="S14" s="107" t="s">
         <v>349</v>
-      </c>
-      <c r="N14" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="O14" s="108" t="s">
-        <v>347</v>
-      </c>
-      <c r="P14" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="Q14" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="R14" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="S14" s="107" t="s">
-        <v>347</v>
       </c>
       <c r="T14" s="107" t="s">
         <v>347</v>
@@ -5528,16 +5528,16 @@
         <v>348</v>
       </c>
       <c r="P15" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q15" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="R15" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="S15" s="107" t="s">
         <v>349</v>
-      </c>
-      <c r="Q15" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="R15" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="S15" s="107" t="s">
-        <v>347</v>
       </c>
       <c r="T15" s="107" t="s">
         <v>347</v>
@@ -5600,16 +5600,16 @@
         <v>348</v>
       </c>
       <c r="P16" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q16" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="R16" s="109" t="s">
+        <v>348</v>
+      </c>
+      <c r="S16" s="107" t="s">
         <v>349</v>
-      </c>
-      <c r="Q16" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="R16" s="109" t="s">
-        <v>348</v>
-      </c>
-      <c r="S16" s="107" t="s">
-        <v>347</v>
       </c>
       <c r="T16" s="107" t="s">
         <v>347</v>
@@ -5660,28 +5660,28 @@
         <v>348</v>
       </c>
       <c r="L17" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="M17" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="N17" s="107" t="s">
+        <v>347</v>
+      </c>
+      <c r="O17" s="108" t="s">
+        <v>347</v>
+      </c>
+      <c r="P17" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q17" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="R17" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="S17" s="107" t="s">
         <v>349</v>
-      </c>
-      <c r="M17" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="N17" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="O17" s="108" t="s">
-        <v>347</v>
-      </c>
-      <c r="P17" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="Q17" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="R17" s="107" t="s">
-        <v>347</v>
-      </c>
-      <c r="S17" s="107" t="s">
-        <v>347</v>
       </c>
       <c r="T17" s="107" t="s">
         <v>347</v>
@@ -6354,11 +6354,7 @@
       <c r="X27" s="106"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X27" xr:uid="{ED25CF60-E519-46A5-8820-1361CFDEEEDA}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X17">
-      <sortCondition descending="1" ref="A1:A27"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:X27" xr:uid="{ED25CF60-E519-46A5-8820-1361CFDEEEDA}"/>
   <conditionalFormatting sqref="H2:V27">
     <cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="Planned">
       <formula>NOT(ISERROR(SEARCH("Planned",H2)))</formula>
